--- a/depo/yerlesim.xlsx
+++ b/depo/yerlesim.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bobın.ambar\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bobın.ambar\Desktop\Yerleşim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACCE69ED-36C2-4D78-8D02-EB6C21B18307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E6BC073-2B29-4769-AE22-E7B291BE456F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="148">
   <si>
     <t>F BLOK</t>
   </si>
@@ -194,6 +194,9 @@
     <t>TLN 140/2050</t>
   </si>
   <si>
+    <t>PFLT 150/2450</t>
+  </si>
+  <si>
     <t>PFLT 150/2500</t>
   </si>
   <si>
@@ -209,6 +212,9 @@
     <t>PFLT 125/2250</t>
   </si>
   <si>
+    <t>PFLT 125/2450</t>
+  </si>
+  <si>
     <t>IKL 135/2500</t>
   </si>
   <si>
@@ -221,6 +227,9 @@
     <t>PFLT 125/2050</t>
   </si>
   <si>
+    <t>PFLT 175/2450</t>
+  </si>
+  <si>
     <t>PFLT 175/2250</t>
   </si>
   <si>
@@ -242,15 +251,24 @@
     <t>FLT 80/1750</t>
   </si>
   <si>
+    <t>FLT 75/2500</t>
+  </si>
+  <si>
     <t>FLT 110/2050</t>
   </si>
   <si>
+    <t>PFLT 110/2500</t>
+  </si>
+  <si>
     <t>TLN 90/1750</t>
   </si>
   <si>
     <t>IKL 175/2250</t>
   </si>
   <si>
+    <t>IKL 175/2450</t>
+  </si>
+  <si>
     <t>IKL 110/1750</t>
   </si>
   <si>
@@ -266,12 +284,21 @@
     <t>KLN 125/2050</t>
   </si>
   <si>
+    <t>KLN 100/1750</t>
+  </si>
+  <si>
     <t>KLN 100/2050</t>
   </si>
   <si>
     <t>KLN 100/2250</t>
   </si>
   <si>
+    <t>KLN 100/2450</t>
+  </si>
+  <si>
+    <t>KLN 135/2450</t>
+  </si>
+  <si>
     <t>KLN 135/2050</t>
   </si>
   <si>
@@ -281,12 +308,21 @@
     <t>IKL 175/2050</t>
   </si>
   <si>
+    <t>IKL 175/2500</t>
+  </si>
+  <si>
     <t>KLN 186/2450</t>
   </si>
   <si>
     <t>FLT 135/1750</t>
   </si>
   <si>
+    <t>TLN 140/2450</t>
+  </si>
+  <si>
+    <t>TLN 140//2250</t>
+  </si>
+  <si>
     <t>SON GÜNCELLEME</t>
   </si>
   <si>
@@ -305,9 +341,21 @@
     <t>TLN 80/2500</t>
   </si>
   <si>
+    <t>TLN 100/2500</t>
+  </si>
+  <si>
+    <t>TLN 100/2250</t>
+  </si>
+  <si>
     <t>FLT 135/2500</t>
   </si>
   <si>
+    <t>FLT 110/2500</t>
+  </si>
+  <si>
+    <t>TLN 100 2500</t>
+  </si>
+  <si>
     <t>TLN 90/2050</t>
   </si>
   <si>
@@ -326,6 +374,9 @@
     <t>FLT 110/2250</t>
   </si>
   <si>
+    <t>TLN 135/2500</t>
+  </si>
+  <si>
     <t>TLN 110/2250</t>
   </si>
   <si>
@@ -338,40 +389,97 @@
     <t>TLN 110/2500</t>
   </si>
   <si>
-    <t>KLN 135/2500</t>
-  </si>
-  <si>
-    <t>IKL 110/2500</t>
-  </si>
-  <si>
-    <t>FLT 135/2350</t>
-  </si>
-  <si>
-    <t>IKL 110/2350</t>
-  </si>
-  <si>
-    <t>BTL 120/2500</t>
-  </si>
-  <si>
-    <t>FLT 135/2050</t>
-  </si>
-  <si>
-    <t>TLN90/2050</t>
-  </si>
-  <si>
-    <t>TLN 110/2050</t>
-  </si>
-  <si>
-    <t>TLN 140/2500</t>
-  </si>
-  <si>
-    <t>KLN 110/2050</t>
-  </si>
-  <si>
-    <t>FLT 80/2350</t>
-  </si>
-  <si>
-    <t>KLN 110/2500</t>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>D7</t>
+  </si>
+  <si>
+    <t>D8</t>
+  </si>
+  <si>
+    <t>D9</t>
+  </si>
+  <si>
+    <t>D10</t>
+  </si>
+  <si>
+    <t>D11</t>
+  </si>
+  <si>
+    <t>D12</t>
+  </si>
+  <si>
+    <t>D13</t>
+  </si>
+  <si>
+    <t>D14</t>
+  </si>
+  <si>
+    <t>D15</t>
+  </si>
+  <si>
+    <t>D16</t>
+  </si>
+  <si>
+    <t>D17</t>
+  </si>
+  <si>
+    <t>D18</t>
+  </si>
+  <si>
+    <t>D19</t>
+  </si>
+  <si>
+    <t>D20</t>
+  </si>
+  <si>
+    <t>D21</t>
+  </si>
+  <si>
+    <t>D22</t>
+  </si>
+  <si>
+    <t>D23</t>
+  </si>
+  <si>
+    <t>D24</t>
+  </si>
+  <si>
+    <t>D25</t>
+  </si>
+  <si>
+    <t>D26</t>
+  </si>
+  <si>
+    <t>D27</t>
+  </si>
+  <si>
+    <t>D28</t>
+  </si>
+  <si>
+    <t>D29</t>
+  </si>
+  <si>
+    <t>D30</t>
   </si>
 </sst>
 </file>
@@ -518,7 +626,7 @@
       <charset val="162"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -573,8 +681,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="52">
+  <borders count="53">
     <border>
       <left/>
       <right/>
@@ -1231,11 +1345,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="219">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1251,7 +1376,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1287,9 +1411,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1335,33 +1456,423 @@
     <xf numFmtId="0" fontId="15" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="14" fontId="15" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -1371,285 +1882,73 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFBDD7EE"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1950,7 +2249,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BU2566"/>
+  <dimension ref="A1:BU2571"/>
   <sheetFormatPr defaultColWidth="5.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1"/>
@@ -1959,780 +2258,780 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:73" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="38"/>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="89" t="s">
+      <c r="A1" s="36"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="174" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="90"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="89" t="s">
+      <c r="G1" s="175"/>
+      <c r="H1" s="176"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="174" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="90"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="32"/>
-      <c r="AC1" s="32"/>
-      <c r="AD1" s="56" t="s">
-        <v>83</v>
-      </c>
-      <c r="AE1" s="56"/>
-      <c r="AF1" s="56"/>
-      <c r="AG1" s="56"/>
-      <c r="AH1" s="56"/>
-      <c r="AI1" s="56"/>
-      <c r="AJ1" s="56"/>
-      <c r="AK1" s="54" t="s">
-        <v>84</v>
-      </c>
-      <c r="AL1" s="55">
-        <v>46034</v>
-      </c>
-      <c r="AM1" s="55"/>
-      <c r="AN1" s="55"/>
-      <c r="AO1" s="55"/>
-      <c r="AP1" s="55"/>
-      <c r="AQ1" s="32"/>
-      <c r="AR1" s="32"/>
-      <c r="AS1" s="50"/>
-      <c r="AT1" s="32"/>
-      <c r="AU1" s="32"/>
-      <c r="AV1" s="32"/>
-      <c r="AW1" s="32"/>
-      <c r="AX1" s="32"/>
-      <c r="AY1" s="32"/>
-      <c r="AZ1" s="32"/>
-      <c r="BA1" s="32"/>
-      <c r="BB1" s="32"/>
-      <c r="BC1" s="32"/>
-      <c r="BD1" s="32"/>
-      <c r="BE1" s="32"/>
-      <c r="BF1" s="32"/>
-      <c r="BG1" s="32"/>
-      <c r="BH1" s="32"/>
-      <c r="BI1" s="32"/>
-      <c r="BJ1" s="32"/>
-      <c r="BK1" s="32"/>
-      <c r="BL1" s="32"/>
-      <c r="BM1" s="32"/>
-      <c r="BN1" s="32"/>
-      <c r="BO1" s="32"/>
-      <c r="BP1" s="32"/>
-      <c r="BQ1" s="32"/>
-      <c r="BR1" s="32"/>
-      <c r="BS1" s="32"/>
-      <c r="BT1" s="33"/>
-      <c r="BU1" s="33"/>
+      <c r="N1" s="175"/>
+      <c r="O1" s="176"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="30"/>
+      <c r="S1" s="30"/>
+      <c r="T1" s="30"/>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
+      <c r="W1" s="30"/>
+      <c r="X1" s="30"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="30"/>
+      <c r="AA1" s="30"/>
+      <c r="AB1" s="30"/>
+      <c r="AC1" s="30"/>
+      <c r="AD1" s="191" t="s">
+        <v>95</v>
+      </c>
+      <c r="AE1" s="191"/>
+      <c r="AF1" s="191"/>
+      <c r="AG1" s="191"/>
+      <c r="AH1" s="191"/>
+      <c r="AI1" s="191"/>
+      <c r="AJ1" s="191"/>
+      <c r="AK1" s="52" t="s">
+        <v>96</v>
+      </c>
+      <c r="AL1" s="190">
+        <v>45917</v>
+      </c>
+      <c r="AM1" s="190"/>
+      <c r="AN1" s="190"/>
+      <c r="AO1" s="190"/>
+      <c r="AP1" s="190"/>
+      <c r="AQ1" s="30"/>
+      <c r="AR1" s="30"/>
+      <c r="AS1" s="48"/>
+      <c r="AT1" s="30"/>
+      <c r="AU1" s="30"/>
+      <c r="AV1" s="30"/>
+      <c r="AW1" s="30"/>
+      <c r="AX1" s="30"/>
+      <c r="AY1" s="30"/>
+      <c r="AZ1" s="30"/>
+      <c r="BA1" s="30"/>
+      <c r="BB1" s="30"/>
+      <c r="BC1" s="30"/>
+      <c r="BD1" s="30"/>
+      <c r="BE1" s="30"/>
+      <c r="BF1" s="30"/>
+      <c r="BG1" s="30"/>
+      <c r="BH1" s="30"/>
+      <c r="BI1" s="30"/>
+      <c r="BJ1" s="30"/>
+      <c r="BK1" s="30"/>
+      <c r="BL1" s="30"/>
+      <c r="BM1" s="30"/>
+      <c r="BN1" s="30"/>
+      <c r="BO1" s="30"/>
+      <c r="BP1" s="30"/>
+      <c r="BQ1" s="30"/>
+      <c r="BR1" s="30"/>
+      <c r="BS1" s="30"/>
+      <c r="BT1" s="31"/>
+      <c r="BU1" s="31"/>
     </row>
     <row r="2" spans="1:73" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="39"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="19"/>
+      <c r="A2" s="37"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="18"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
-      <c r="K2" s="100"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="95"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="95"/>
-      <c r="P2" s="95"/>
-      <c r="Q2" s="95"/>
-      <c r="R2" s="95"/>
-      <c r="S2" s="95"/>
-      <c r="T2" s="95" t="s">
-        <v>108</v>
-      </c>
-      <c r="U2" s="95" t="s">
-        <v>97</v>
-      </c>
-      <c r="V2" s="95" t="s">
-        <v>97</v>
-      </c>
-      <c r="W2" s="107" t="s">
-        <v>51</v>
-      </c>
-      <c r="X2" s="98" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y2" s="98" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z2" s="62" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA2" s="62" t="s">
-        <v>110</v>
-      </c>
-      <c r="AB2" s="76" t="s">
-        <v>110</v>
-      </c>
-      <c r="AC2" s="64" t="s">
+      <c r="K2" s="180"/>
+      <c r="L2" s="177"/>
+      <c r="M2" s="162"/>
+      <c r="N2" s="162" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" s="162" t="s">
+        <v>61</v>
+      </c>
+      <c r="P2" s="162"/>
+      <c r="Q2" s="162" t="s">
+        <v>60</v>
+      </c>
+      <c r="R2" s="162" t="s">
+        <v>61</v>
+      </c>
+      <c r="S2" s="162"/>
+      <c r="T2" s="162" t="s">
+        <v>59</v>
+      </c>
+      <c r="U2" s="162" t="s">
+        <v>58</v>
+      </c>
+      <c r="V2" s="162" t="s">
+        <v>109</v>
+      </c>
+      <c r="W2" s="166" t="s">
+        <v>101</v>
+      </c>
+      <c r="X2" s="168" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y2" s="168" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z2" s="103" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA2" s="103" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB2" s="115" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC2" s="192" t="s">
         <v>11</v>
       </c>
-      <c r="AD2" s="59" t="s">
+      <c r="AD2" s="153"/>
+      <c r="AE2" s="103" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF2" s="103"/>
+      <c r="AG2" s="103" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH2" s="103" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI2" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ2" s="103" t="s">
+        <v>58</v>
+      </c>
+      <c r="AK2" s="103" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL2" s="103" t="s">
+        <v>77</v>
+      </c>
+      <c r="AM2" s="103"/>
+      <c r="AN2" s="103" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO2" s="103" t="s">
+        <v>67</v>
+      </c>
+      <c r="AP2" s="103"/>
+      <c r="AQ2" s="103" t="s">
+        <v>58</v>
+      </c>
+      <c r="AR2" s="103" t="s">
+        <v>89</v>
+      </c>
+      <c r="AS2" s="103" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT2" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="AU2" s="103" t="s">
+        <v>86</v>
+      </c>
+      <c r="AV2" s="103" t="s">
+        <v>86</v>
+      </c>
+      <c r="AW2" s="103" t="s">
+        <v>85</v>
+      </c>
+      <c r="AX2" s="103" t="s">
+        <v>84</v>
+      </c>
+      <c r="AY2" s="103" t="s">
+        <v>83</v>
+      </c>
+      <c r="AZ2" s="115" t="s">
+        <v>82</v>
+      </c>
+      <c r="BA2" s="183" t="s">
+        <v>11</v>
+      </c>
+      <c r="BB2" s="153" t="s">
         <v>81</v>
       </c>
-      <c r="AE2" s="62" t="s">
-        <v>111</v>
-      </c>
-      <c r="AF2" s="62" t="s">
+      <c r="BC2" s="103" t="s">
+        <v>81</v>
+      </c>
+      <c r="BD2" s="103" t="s">
+        <v>59</v>
+      </c>
+      <c r="BE2" s="103" t="s">
+        <v>59</v>
+      </c>
+      <c r="BF2" s="103" t="s">
+        <v>107</v>
+      </c>
+      <c r="BG2" s="103" t="s">
+        <v>107</v>
+      </c>
+      <c r="BH2" s="103" t="s">
+        <v>80</v>
+      </c>
+      <c r="BI2" s="103" t="s">
+        <v>80</v>
+      </c>
+      <c r="BJ2" s="103"/>
+      <c r="BK2" s="103"/>
+      <c r="BL2" s="103"/>
+      <c r="BM2" s="103" t="s">
+        <v>79</v>
+      </c>
+      <c r="BN2" s="103" t="s">
+        <v>79</v>
+      </c>
+      <c r="BO2" s="103" t="s">
+        <v>78</v>
+      </c>
+      <c r="BP2" s="103" t="s">
         <v>77</v>
       </c>
-      <c r="AG2" s="62" t="s">
+      <c r="BQ2" s="103" t="s">
         <v>76</v>
       </c>
-      <c r="AH2" s="62" t="s">
+      <c r="BR2" s="115" t="s">
         <v>75</v>
-      </c>
-      <c r="AI2" s="62" t="s">
-        <v>75</v>
-      </c>
-      <c r="AJ2" s="62"/>
-      <c r="AK2" s="62" t="s">
-        <v>77</v>
-      </c>
-      <c r="AL2" s="62" t="s">
-        <v>76</v>
-      </c>
-      <c r="AM2" s="62"/>
-      <c r="AN2" s="62" t="s">
-        <v>79</v>
-      </c>
-      <c r="AO2" s="62" t="s">
-        <v>100</v>
-      </c>
-      <c r="AP2" s="62" t="s">
-        <v>79</v>
-      </c>
-      <c r="AQ2" s="62" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR2" s="62" t="s">
-        <v>78</v>
-      </c>
-      <c r="AS2" s="62" t="s">
-        <v>79</v>
-      </c>
-      <c r="AT2" s="62"/>
-      <c r="AU2" s="62"/>
-      <c r="AV2" s="62" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW2" s="62" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX2" s="62" t="s">
-        <v>101</v>
-      </c>
-      <c r="AY2" s="62" t="s">
-        <v>101</v>
-      </c>
-      <c r="AZ2" s="76" t="s">
-        <v>55</v>
-      </c>
-      <c r="BA2" s="72" t="s">
-        <v>11</v>
-      </c>
-      <c r="BB2" s="59" t="s">
-        <v>101</v>
-      </c>
-      <c r="BC2" s="62" t="s">
-        <v>101</v>
-      </c>
-      <c r="BD2" s="62" t="s">
-        <v>73</v>
-      </c>
-      <c r="BE2" s="62" t="s">
-        <v>73</v>
-      </c>
-      <c r="BF2" s="62" t="s">
-        <v>72</v>
-      </c>
-      <c r="BG2" s="62" t="s">
-        <v>72</v>
-      </c>
-      <c r="BH2" s="62" t="s">
-        <v>57</v>
-      </c>
-      <c r="BI2" s="62" t="s">
-        <v>57</v>
-      </c>
-      <c r="BJ2" s="62" t="s">
-        <v>91</v>
-      </c>
-      <c r="BK2" s="62" t="s">
-        <v>91</v>
-      </c>
-      <c r="BL2" s="62"/>
-      <c r="BM2" s="62" t="s">
-        <v>74</v>
-      </c>
-      <c r="BN2" s="62" t="s">
-        <v>74</v>
-      </c>
-      <c r="BO2" s="62" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP2" s="62" t="s">
-        <v>80</v>
-      </c>
-      <c r="BQ2" s="62" t="s">
-        <v>80</v>
-      </c>
-      <c r="BR2" s="76" t="s">
-        <v>70</v>
       </c>
       <c r="BS2" s="2"/>
       <c r="BT2" s="3"/>
-      <c r="BU2" s="37"/>
+      <c r="BU2" s="35"/>
     </row>
     <row r="3" spans="1:73" ht="29.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="39"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="21"/>
-      <c r="K3" s="101"/>
-      <c r="L3" s="93"/>
-      <c r="M3" s="96"/>
-      <c r="N3" s="96"/>
-      <c r="O3" s="96"/>
-      <c r="P3" s="96"/>
-      <c r="Q3" s="96"/>
-      <c r="R3" s="96"/>
-      <c r="S3" s="96"/>
-      <c r="T3" s="96"/>
-      <c r="U3" s="96"/>
-      <c r="V3" s="96"/>
-      <c r="W3" s="108"/>
-      <c r="X3" s="99"/>
-      <c r="Y3" s="99"/>
-      <c r="Z3" s="63"/>
-      <c r="AA3" s="63"/>
-      <c r="AB3" s="77"/>
-      <c r="AC3" s="65"/>
-      <c r="AD3" s="60"/>
-      <c r="AE3" s="63"/>
-      <c r="AF3" s="63"/>
-      <c r="AG3" s="63"/>
-      <c r="AH3" s="63"/>
-      <c r="AI3" s="63"/>
-      <c r="AJ3" s="63"/>
-      <c r="AK3" s="63"/>
-      <c r="AL3" s="63"/>
-      <c r="AM3" s="63"/>
-      <c r="AN3" s="63"/>
-      <c r="AO3" s="63"/>
-      <c r="AP3" s="63"/>
-      <c r="AQ3" s="63"/>
-      <c r="AR3" s="63"/>
-      <c r="AS3" s="63"/>
-      <c r="AT3" s="63"/>
-      <c r="AU3" s="63"/>
-      <c r="AV3" s="63"/>
-      <c r="AW3" s="63"/>
-      <c r="AX3" s="63"/>
-      <c r="AY3" s="63"/>
-      <c r="AZ3" s="77"/>
-      <c r="BA3" s="73"/>
-      <c r="BB3" s="60"/>
-      <c r="BC3" s="63"/>
-      <c r="BD3" s="63"/>
-      <c r="BE3" s="63"/>
-      <c r="BF3" s="63"/>
-      <c r="BG3" s="63"/>
-      <c r="BH3" s="63"/>
-      <c r="BI3" s="63"/>
-      <c r="BJ3" s="63"/>
-      <c r="BK3" s="63"/>
-      <c r="BL3" s="63"/>
-      <c r="BM3" s="63"/>
-      <c r="BN3" s="63"/>
-      <c r="BO3" s="63"/>
-      <c r="BP3" s="63"/>
-      <c r="BQ3" s="63"/>
-      <c r="BR3" s="77"/>
+      <c r="A3" s="37"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="20"/>
+      <c r="K3" s="181"/>
+      <c r="L3" s="178"/>
+      <c r="M3" s="163"/>
+      <c r="N3" s="163"/>
+      <c r="O3" s="163"/>
+      <c r="P3" s="163"/>
+      <c r="Q3" s="163"/>
+      <c r="R3" s="163"/>
+      <c r="S3" s="163"/>
+      <c r="T3" s="163"/>
+      <c r="U3" s="163"/>
+      <c r="V3" s="163"/>
+      <c r="W3" s="167"/>
+      <c r="X3" s="169"/>
+      <c r="Y3" s="169"/>
+      <c r="Z3" s="104"/>
+      <c r="AA3" s="104"/>
+      <c r="AB3" s="116"/>
+      <c r="AC3" s="193"/>
+      <c r="AD3" s="154"/>
+      <c r="AE3" s="104"/>
+      <c r="AF3" s="104"/>
+      <c r="AG3" s="104"/>
+      <c r="AH3" s="104"/>
+      <c r="AI3" s="104"/>
+      <c r="AJ3" s="104"/>
+      <c r="AK3" s="104"/>
+      <c r="AL3" s="104"/>
+      <c r="AM3" s="104"/>
+      <c r="AN3" s="104"/>
+      <c r="AO3" s="104"/>
+      <c r="AP3" s="104"/>
+      <c r="AQ3" s="104"/>
+      <c r="AR3" s="104"/>
+      <c r="AS3" s="104"/>
+      <c r="AT3" s="104"/>
+      <c r="AU3" s="104"/>
+      <c r="AV3" s="104"/>
+      <c r="AW3" s="104"/>
+      <c r="AX3" s="104"/>
+      <c r="AY3" s="104"/>
+      <c r="AZ3" s="116"/>
+      <c r="BA3" s="184"/>
+      <c r="BB3" s="154"/>
+      <c r="BC3" s="104"/>
+      <c r="BD3" s="104"/>
+      <c r="BE3" s="104"/>
+      <c r="BF3" s="104"/>
+      <c r="BG3" s="104"/>
+      <c r="BH3" s="104"/>
+      <c r="BI3" s="104"/>
+      <c r="BJ3" s="104"/>
+      <c r="BK3" s="104"/>
+      <c r="BL3" s="104"/>
+      <c r="BM3" s="104"/>
+      <c r="BN3" s="104"/>
+      <c r="BO3" s="104"/>
+      <c r="BP3" s="104"/>
+      <c r="BQ3" s="104"/>
+      <c r="BR3" s="116"/>
       <c r="BT3" s="4"/>
-      <c r="BU3" s="37"/>
+      <c r="BU3" s="35"/>
     </row>
     <row r="4" spans="1:73" ht="29.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="39"/>
-      <c r="B4" s="86" t="s">
+      <c r="A4" s="37"/>
+      <c r="B4" s="171" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="87"/>
-      <c r="D4" s="88"/>
-      <c r="K4" s="101"/>
-      <c r="L4" s="93"/>
-      <c r="M4" s="96"/>
-      <c r="N4" s="96"/>
-      <c r="O4" s="96"/>
-      <c r="P4" s="96"/>
-      <c r="Q4" s="96"/>
-      <c r="R4" s="96"/>
-      <c r="S4" s="96"/>
-      <c r="T4" s="96"/>
-      <c r="U4" s="96"/>
-      <c r="V4" s="96"/>
-      <c r="W4" s="108"/>
-      <c r="X4" s="99"/>
-      <c r="Y4" s="99"/>
-      <c r="Z4" s="63"/>
-      <c r="AA4" s="63"/>
-      <c r="AB4" s="77"/>
-      <c r="AC4" s="65"/>
-      <c r="AD4" s="60"/>
-      <c r="AE4" s="63"/>
-      <c r="AF4" s="63"/>
-      <c r="AG4" s="63"/>
-      <c r="AH4" s="63"/>
-      <c r="AI4" s="63"/>
-      <c r="AJ4" s="63"/>
-      <c r="AK4" s="63"/>
-      <c r="AL4" s="63"/>
-      <c r="AM4" s="63"/>
-      <c r="AN4" s="63"/>
-      <c r="AO4" s="63"/>
-      <c r="AP4" s="63"/>
-      <c r="AQ4" s="63"/>
-      <c r="AR4" s="63"/>
-      <c r="AS4" s="63"/>
-      <c r="AT4" s="63"/>
-      <c r="AU4" s="63"/>
-      <c r="AV4" s="63"/>
-      <c r="AW4" s="63"/>
-      <c r="AX4" s="63"/>
-      <c r="AY4" s="63"/>
-      <c r="AZ4" s="77"/>
-      <c r="BA4" s="73"/>
-      <c r="BB4" s="60"/>
-      <c r="BC4" s="63"/>
-      <c r="BD4" s="63"/>
-      <c r="BE4" s="63"/>
-      <c r="BF4" s="63"/>
-      <c r="BG4" s="63"/>
-      <c r="BH4" s="63"/>
-      <c r="BI4" s="63"/>
-      <c r="BJ4" s="63"/>
-      <c r="BK4" s="63"/>
-      <c r="BL4" s="63"/>
-      <c r="BM4" s="63"/>
-      <c r="BN4" s="63"/>
-      <c r="BO4" s="63"/>
-      <c r="BP4" s="63"/>
-      <c r="BQ4" s="63"/>
-      <c r="BR4" s="77"/>
+      <c r="C4" s="172"/>
+      <c r="D4" s="173"/>
+      <c r="K4" s="181"/>
+      <c r="L4" s="178"/>
+      <c r="M4" s="163"/>
+      <c r="N4" s="163"/>
+      <c r="O4" s="163"/>
+      <c r="P4" s="163"/>
+      <c r="Q4" s="163"/>
+      <c r="R4" s="163"/>
+      <c r="S4" s="163"/>
+      <c r="T4" s="163"/>
+      <c r="U4" s="163"/>
+      <c r="V4" s="163"/>
+      <c r="W4" s="167"/>
+      <c r="X4" s="169"/>
+      <c r="Y4" s="169"/>
+      <c r="Z4" s="104"/>
+      <c r="AA4" s="104"/>
+      <c r="AB4" s="116"/>
+      <c r="AC4" s="193"/>
+      <c r="AD4" s="154"/>
+      <c r="AE4" s="104"/>
+      <c r="AF4" s="104"/>
+      <c r="AG4" s="104"/>
+      <c r="AH4" s="104"/>
+      <c r="AI4" s="104"/>
+      <c r="AJ4" s="104"/>
+      <c r="AK4" s="104"/>
+      <c r="AL4" s="104"/>
+      <c r="AM4" s="104"/>
+      <c r="AN4" s="104"/>
+      <c r="AO4" s="104"/>
+      <c r="AP4" s="104"/>
+      <c r="AQ4" s="104"/>
+      <c r="AR4" s="104"/>
+      <c r="AS4" s="104"/>
+      <c r="AT4" s="104"/>
+      <c r="AU4" s="104"/>
+      <c r="AV4" s="104"/>
+      <c r="AW4" s="104"/>
+      <c r="AX4" s="104"/>
+      <c r="AY4" s="104"/>
+      <c r="AZ4" s="116"/>
+      <c r="BA4" s="184"/>
+      <c r="BB4" s="154"/>
+      <c r="BC4" s="104"/>
+      <c r="BD4" s="104"/>
+      <c r="BE4" s="104"/>
+      <c r="BF4" s="104"/>
+      <c r="BG4" s="104"/>
+      <c r="BH4" s="104"/>
+      <c r="BI4" s="104"/>
+      <c r="BJ4" s="104"/>
+      <c r="BK4" s="104"/>
+      <c r="BL4" s="104"/>
+      <c r="BM4" s="104"/>
+      <c r="BN4" s="104"/>
+      <c r="BO4" s="104"/>
+      <c r="BP4" s="104"/>
+      <c r="BQ4" s="104"/>
+      <c r="BR4" s="116"/>
       <c r="BT4" s="4"/>
-      <c r="BU4" s="37"/>
+      <c r="BU4" s="35"/>
     </row>
     <row r="5" spans="1:73" ht="29.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="39"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="21"/>
-      <c r="K5" s="102"/>
-      <c r="L5" s="94"/>
-      <c r="M5" s="97"/>
-      <c r="N5" s="97"/>
-      <c r="O5" s="97"/>
-      <c r="P5" s="97"/>
-      <c r="Q5" s="97"/>
-      <c r="R5" s="97"/>
-      <c r="S5" s="97"/>
-      <c r="T5" s="97"/>
-      <c r="U5" s="97"/>
-      <c r="V5" s="97"/>
-      <c r="W5" s="108"/>
-      <c r="X5" s="99"/>
-      <c r="Y5" s="99"/>
-      <c r="Z5" s="63"/>
-      <c r="AA5" s="63"/>
-      <c r="AB5" s="77"/>
-      <c r="AC5" s="65"/>
-      <c r="AD5" s="60"/>
-      <c r="AE5" s="63"/>
-      <c r="AF5" s="63"/>
-      <c r="AG5" s="63"/>
-      <c r="AH5" s="63"/>
-      <c r="AI5" s="63"/>
-      <c r="AJ5" s="63"/>
-      <c r="AK5" s="63"/>
-      <c r="AL5" s="63"/>
-      <c r="AM5" s="63"/>
-      <c r="AN5" s="63"/>
-      <c r="AO5" s="63"/>
-      <c r="AP5" s="63"/>
-      <c r="AQ5" s="63"/>
-      <c r="AR5" s="63"/>
-      <c r="AS5" s="63"/>
-      <c r="AT5" s="63"/>
-      <c r="AU5" s="63"/>
-      <c r="AV5" s="63"/>
-      <c r="AW5" s="63"/>
-      <c r="AX5" s="63"/>
-      <c r="AY5" s="63"/>
-      <c r="AZ5" s="77"/>
-      <c r="BA5" s="73"/>
-      <c r="BB5" s="60"/>
-      <c r="BC5" s="63"/>
-      <c r="BD5" s="63"/>
-      <c r="BE5" s="63"/>
-      <c r="BF5" s="63"/>
-      <c r="BG5" s="63"/>
-      <c r="BH5" s="63"/>
-      <c r="BI5" s="63"/>
-      <c r="BJ5" s="63"/>
-      <c r="BK5" s="63"/>
-      <c r="BL5" s="63"/>
-      <c r="BM5" s="63"/>
-      <c r="BN5" s="63"/>
-      <c r="BO5" s="63"/>
-      <c r="BP5" s="63"/>
-      <c r="BQ5" s="63"/>
-      <c r="BR5" s="77"/>
+      <c r="A5" s="37"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="20"/>
+      <c r="K5" s="182"/>
+      <c r="L5" s="179"/>
+      <c r="M5" s="164"/>
+      <c r="N5" s="164"/>
+      <c r="O5" s="164"/>
+      <c r="P5" s="164"/>
+      <c r="Q5" s="164"/>
+      <c r="R5" s="164"/>
+      <c r="S5" s="164"/>
+      <c r="T5" s="164"/>
+      <c r="U5" s="164"/>
+      <c r="V5" s="164"/>
+      <c r="W5" s="167"/>
+      <c r="X5" s="169"/>
+      <c r="Y5" s="169"/>
+      <c r="Z5" s="104"/>
+      <c r="AA5" s="104"/>
+      <c r="AB5" s="116"/>
+      <c r="AC5" s="193"/>
+      <c r="AD5" s="154"/>
+      <c r="AE5" s="104"/>
+      <c r="AF5" s="104"/>
+      <c r="AG5" s="104"/>
+      <c r="AH5" s="104"/>
+      <c r="AI5" s="104"/>
+      <c r="AJ5" s="104"/>
+      <c r="AK5" s="104"/>
+      <c r="AL5" s="104"/>
+      <c r="AM5" s="104"/>
+      <c r="AN5" s="104"/>
+      <c r="AO5" s="104"/>
+      <c r="AP5" s="104"/>
+      <c r="AQ5" s="104"/>
+      <c r="AR5" s="104"/>
+      <c r="AS5" s="104"/>
+      <c r="AT5" s="104"/>
+      <c r="AU5" s="104"/>
+      <c r="AV5" s="104"/>
+      <c r="AW5" s="104"/>
+      <c r="AX5" s="104"/>
+      <c r="AY5" s="104"/>
+      <c r="AZ5" s="116"/>
+      <c r="BA5" s="184"/>
+      <c r="BB5" s="154"/>
+      <c r="BC5" s="104"/>
+      <c r="BD5" s="104"/>
+      <c r="BE5" s="104"/>
+      <c r="BF5" s="104"/>
+      <c r="BG5" s="104"/>
+      <c r="BH5" s="104"/>
+      <c r="BI5" s="104"/>
+      <c r="BJ5" s="104"/>
+      <c r="BK5" s="104"/>
+      <c r="BL5" s="104"/>
+      <c r="BM5" s="104"/>
+      <c r="BN5" s="104"/>
+      <c r="BO5" s="104"/>
+      <c r="BP5" s="104"/>
+      <c r="BQ5" s="104"/>
+      <c r="BR5" s="116"/>
       <c r="BT5" s="4"/>
-      <c r="BU5" s="37"/>
+      <c r="BU5" s="35"/>
     </row>
     <row r="6" spans="1:73" ht="29.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="39"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="21"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="K6" s="48" t="s">
+      <c r="A6" s="37"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="20"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="K6" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="41" t="s">
+      <c r="L6" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="M6" s="41" t="s">
+      <c r="M6" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="N6" s="41" t="s">
+      <c r="N6" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="O6" s="41" t="s">
+      <c r="O6" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="P6" s="41" t="s">
+      <c r="P6" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="41" t="s">
+      <c r="Q6" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="R6" s="41" t="s">
+      <c r="R6" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="S6" s="41" t="s">
+      <c r="S6" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="T6" s="41" t="s">
+      <c r="T6" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="U6" s="41" t="s">
+      <c r="U6" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="V6" s="41" t="s">
+      <c r="V6" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="W6" s="42">
+      <c r="W6" s="40">
         <v>1</v>
       </c>
-      <c r="X6" s="42">
+      <c r="X6" s="40">
         <v>2</v>
       </c>
-      <c r="Y6" s="42">
+      <c r="Y6" s="40">
         <v>3</v>
       </c>
-      <c r="Z6" s="42">
+      <c r="Z6" s="40">
         <v>4</v>
       </c>
-      <c r="AA6" s="42">
+      <c r="AA6" s="40">
         <v>5</v>
       </c>
-      <c r="AB6" s="43">
+      <c r="AB6" s="41">
         <v>6</v>
       </c>
-      <c r="AC6" s="66"/>
-      <c r="AD6" s="47">
+      <c r="AC6" s="194"/>
+      <c r="AD6" s="45">
         <v>1</v>
       </c>
-      <c r="AE6" s="42">
+      <c r="AE6" s="40">
         <v>2</v>
       </c>
-      <c r="AF6" s="42">
+      <c r="AF6" s="40">
         <v>3</v>
       </c>
-      <c r="AG6" s="42">
+      <c r="AG6" s="40">
         <v>4</v>
       </c>
-      <c r="AH6" s="42">
+      <c r="AH6" s="40">
         <v>5</v>
       </c>
-      <c r="AI6" s="42">
+      <c r="AI6" s="40">
         <v>6</v>
       </c>
-      <c r="AJ6" s="42">
+      <c r="AJ6" s="40">
         <v>7</v>
       </c>
-      <c r="AK6" s="42">
+      <c r="AK6" s="40">
         <v>8</v>
       </c>
-      <c r="AL6" s="42">
+      <c r="AL6" s="40">
         <v>9</v>
       </c>
-      <c r="AM6" s="42">
+      <c r="AM6" s="40">
         <v>10</v>
       </c>
-      <c r="AN6" s="42">
+      <c r="AN6" s="40">
         <v>11</v>
       </c>
-      <c r="AO6" s="42">
+      <c r="AO6" s="40">
         <v>12</v>
       </c>
-      <c r="AP6" s="42">
+      <c r="AP6" s="40">
         <v>13</v>
       </c>
-      <c r="AQ6" s="42">
+      <c r="AQ6" s="40">
         <v>14</v>
       </c>
-      <c r="AR6" s="42">
+      <c r="AR6" s="40">
         <v>15</v>
       </c>
-      <c r="AS6" s="42">
+      <c r="AS6" s="40">
         <v>16</v>
       </c>
-      <c r="AT6" s="42">
+      <c r="AT6" s="40">
         <v>17</v>
       </c>
-      <c r="AU6" s="42">
+      <c r="AU6" s="40">
         <v>18</v>
       </c>
-      <c r="AV6" s="42">
+      <c r="AV6" s="40">
         <v>19</v>
       </c>
-      <c r="AW6" s="42">
+      <c r="AW6" s="40">
         <v>20</v>
       </c>
-      <c r="AX6" s="42">
+      <c r="AX6" s="40">
         <v>21</v>
       </c>
-      <c r="AY6" s="42">
+      <c r="AY6" s="40">
         <v>22</v>
       </c>
-      <c r="AZ6" s="43">
+      <c r="AZ6" s="41">
         <v>23</v>
       </c>
-      <c r="BA6" s="74"/>
-      <c r="BB6" s="47">
+      <c r="BA6" s="185"/>
+      <c r="BB6" s="45">
         <v>1</v>
       </c>
-      <c r="BC6" s="42">
+      <c r="BC6" s="40">
         <v>2</v>
       </c>
-      <c r="BD6" s="42">
+      <c r="BD6" s="40">
         <v>3</v>
       </c>
-      <c r="BE6" s="42">
+      <c r="BE6" s="40">
         <v>4</v>
       </c>
-      <c r="BF6" s="42">
+      <c r="BF6" s="40">
         <v>5</v>
       </c>
-      <c r="BG6" s="42">
+      <c r="BG6" s="40">
         <v>6</v>
       </c>
-      <c r="BH6" s="42">
+      <c r="BH6" s="40">
         <v>7</v>
       </c>
-      <c r="BI6" s="42">
+      <c r="BI6" s="40">
         <v>8</v>
       </c>
-      <c r="BJ6" s="42">
+      <c r="BJ6" s="40">
         <v>9</v>
       </c>
-      <c r="BK6" s="42">
+      <c r="BK6" s="40">
         <v>10</v>
       </c>
-      <c r="BL6" s="42">
+      <c r="BL6" s="40">
         <v>11</v>
       </c>
-      <c r="BM6" s="42">
+      <c r="BM6" s="40">
         <v>12</v>
       </c>
-      <c r="BN6" s="42">
+      <c r="BN6" s="40">
         <v>13</v>
       </c>
-      <c r="BO6" s="42">
+      <c r="BO6" s="40">
         <v>14</v>
       </c>
-      <c r="BP6" s="42">
+      <c r="BP6" s="40">
         <v>15</v>
       </c>
-      <c r="BQ6" s="42">
+      <c r="BQ6" s="40">
         <v>16</v>
       </c>
-      <c r="BR6" s="43">
+      <c r="BR6" s="41">
         <v>17</v>
       </c>
       <c r="BT6" s="4"/>
-      <c r="BU6" s="37"/>
+      <c r="BU6" s="35"/>
     </row>
     <row r="7" spans="1:73" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="39"/>
-      <c r="B7" s="122" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" s="123"/>
-      <c r="D7" s="123"/>
-      <c r="E7" s="124"/>
-      <c r="F7" s="44" t="s">
+      <c r="A7" s="37"/>
+      <c r="B7" s="144"/>
+      <c r="C7" s="145"/>
+      <c r="D7" s="145"/>
+      <c r="E7" s="146"/>
+      <c r="F7" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="142"/>
-      <c r="I7" s="143"/>
-      <c r="W7" s="106" t="s">
+      <c r="H7" s="121"/>
+      <c r="I7" s="122"/>
+      <c r="W7" s="165" t="s">
         <v>3</v>
       </c>
-      <c r="X7" s="106"/>
-      <c r="Y7" s="106"/>
-      <c r="Z7" s="106"/>
-      <c r="AA7" s="106"/>
-      <c r="AB7" s="106"/>
-      <c r="AD7" s="83" t="s">
+      <c r="X7" s="165"/>
+      <c r="Y7" s="165"/>
+      <c r="Z7" s="165"/>
+      <c r="AA7" s="165"/>
+      <c r="AB7" s="165"/>
+      <c r="AD7" s="111" t="s">
         <v>0</v>
       </c>
-      <c r="AE7" s="83"/>
-      <c r="AF7" s="83"/>
-      <c r="AG7" s="83"/>
-      <c r="AH7" s="83"/>
-      <c r="AI7" s="83"/>
-      <c r="AJ7" s="83"/>
-      <c r="AK7" s="83"/>
-      <c r="AL7" s="83"/>
-      <c r="AM7" s="83"/>
-      <c r="AN7" s="83"/>
-      <c r="AO7" s="83"/>
-      <c r="AP7" s="83"/>
-      <c r="AQ7" s="83"/>
-      <c r="AR7" s="83"/>
-      <c r="AS7" s="83"/>
-      <c r="AT7" s="83"/>
-      <c r="AU7" s="83"/>
-      <c r="AV7" s="83"/>
-      <c r="AW7" s="83"/>
-      <c r="AX7" s="83"/>
-      <c r="AY7" s="83"/>
-      <c r="AZ7" s="83"/>
-      <c r="BB7" s="83" t="s">
+      <c r="AE7" s="111"/>
+      <c r="AF7" s="111"/>
+      <c r="AG7" s="111"/>
+      <c r="AH7" s="111"/>
+      <c r="AI7" s="111"/>
+      <c r="AJ7" s="111"/>
+      <c r="AK7" s="111"/>
+      <c r="AL7" s="111"/>
+      <c r="AM7" s="111"/>
+      <c r="AN7" s="111"/>
+      <c r="AO7" s="111"/>
+      <c r="AP7" s="111"/>
+      <c r="AQ7" s="111"/>
+      <c r="AR7" s="111"/>
+      <c r="AS7" s="111"/>
+      <c r="AT7" s="111"/>
+      <c r="AU7" s="111"/>
+      <c r="AV7" s="111"/>
+      <c r="AW7" s="111"/>
+      <c r="AX7" s="111"/>
+      <c r="AY7" s="111"/>
+      <c r="AZ7" s="111"/>
+      <c r="BB7" s="111" t="s">
         <v>2</v>
       </c>
-      <c r="BC7" s="83"/>
-      <c r="BD7" s="83"/>
-      <c r="BE7" s="83"/>
-      <c r="BF7" s="83"/>
-      <c r="BG7" s="83"/>
-      <c r="BH7" s="83"/>
-      <c r="BI7" s="83"/>
-      <c r="BJ7" s="83"/>
-      <c r="BK7" s="83"/>
-      <c r="BL7" s="83"/>
-      <c r="BM7" s="83"/>
-      <c r="BN7" s="83"/>
-      <c r="BO7" s="83"/>
-      <c r="BP7" s="83"/>
-      <c r="BQ7" s="83"/>
-      <c r="BR7" s="83"/>
+      <c r="BC7" s="111"/>
+      <c r="BD7" s="111"/>
+      <c r="BE7" s="111"/>
+      <c r="BF7" s="111"/>
+      <c r="BG7" s="111"/>
+      <c r="BH7" s="111"/>
+      <c r="BI7" s="111"/>
+      <c r="BJ7" s="111"/>
+      <c r="BK7" s="111"/>
+      <c r="BL7" s="111"/>
+      <c r="BM7" s="111"/>
+      <c r="BN7" s="111"/>
+      <c r="BO7" s="111"/>
+      <c r="BP7" s="111"/>
+      <c r="BQ7" s="111"/>
+      <c r="BR7" s="111"/>
       <c r="BT7" s="4"/>
-      <c r="BU7" s="37"/>
+      <c r="BU7" s="35"/>
     </row>
     <row r="8" spans="1:73" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="39"/>
-      <c r="B8" s="109" t="s">
-        <v>102</v>
-      </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="110"/>
-      <c r="E8" s="111"/>
-      <c r="F8" s="45" t="s">
+      <c r="A8" s="37"/>
+      <c r="B8" s="147"/>
+      <c r="C8" s="148"/>
+      <c r="D8" s="148"/>
+      <c r="E8" s="149"/>
+      <c r="F8" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="103"/>
-      <c r="I8" s="104"/>
-      <c r="V8" s="14"/>
+      <c r="H8" s="110"/>
+      <c r="I8" s="123"/>
+      <c r="V8" s="13"/>
       <c r="BT8" s="4"/>
-      <c r="BU8" s="37"/>
+      <c r="BU8" s="35"/>
     </row>
     <row r="9" spans="1:73" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="39"/>
-      <c r="B9" s="109" t="s">
-        <v>102</v>
-      </c>
-      <c r="C9" s="110"/>
-      <c r="D9" s="110"/>
-      <c r="E9" s="111"/>
-      <c r="F9" s="45" t="s">
+      <c r="A9" s="37"/>
+      <c r="B9" s="147" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="148"/>
+      <c r="D9" s="148"/>
+      <c r="E9" s="149"/>
+      <c r="F9" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="H9" s="70" t="s">
+      <c r="H9" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="144"/>
-      <c r="J9" s="57"/>
-      <c r="K9" s="57"/>
-      <c r="L9" s="57"/>
-      <c r="M9" s="57"/>
-      <c r="N9" s="57"/>
-      <c r="O9" s="57"/>
-      <c r="P9" s="57"/>
-      <c r="Q9" s="57"/>
-      <c r="R9" s="57"/>
-      <c r="S9" s="57"/>
-      <c r="T9" s="57"/>
-      <c r="U9" s="57"/>
-      <c r="V9" s="57"/>
-      <c r="W9" s="57" t="s">
+      <c r="I9" s="125"/>
+      <c r="J9" s="127"/>
+      <c r="K9" s="127"/>
+      <c r="L9" s="127"/>
+      <c r="M9" s="127"/>
+      <c r="N9" s="127"/>
+      <c r="O9" s="127"/>
+      <c r="P9" s="127"/>
+      <c r="Q9" s="127"/>
+      <c r="R9" s="127"/>
+      <c r="S9" s="127"/>
+      <c r="T9" s="127"/>
+      <c r="U9" s="127"/>
+      <c r="V9" s="127"/>
+      <c r="W9" s="127" t="s">
         <v>7</v>
       </c>
-      <c r="X9" s="57"/>
-      <c r="Y9" s="57"/>
-      <c r="Z9" s="57"/>
-      <c r="AA9" s="57"/>
-      <c r="AB9" s="57"/>
-      <c r="AC9" s="57"/>
-      <c r="AD9" s="57"/>
-      <c r="AE9" s="57"/>
-      <c r="AF9" s="57"/>
-      <c r="AG9" s="57"/>
-      <c r="AH9" s="57"/>
-      <c r="AI9" s="57"/>
-      <c r="AJ9" s="57"/>
-      <c r="AK9" s="57"/>
-      <c r="AL9" s="57"/>
+      <c r="X9" s="127"/>
+      <c r="Y9" s="127"/>
+      <c r="Z9" s="127"/>
+      <c r="AA9" s="127"/>
+      <c r="AB9" s="127"/>
+      <c r="AC9" s="127"/>
+      <c r="AD9" s="127"/>
+      <c r="AE9" s="127"/>
+      <c r="AF9" s="127"/>
+      <c r="AG9" s="127"/>
+      <c r="AH9" s="127"/>
+      <c r="AI9" s="127"/>
+      <c r="AJ9" s="127"/>
+      <c r="AK9" s="127"/>
+      <c r="AL9" s="127"/>
       <c r="AM9" s="9"/>
       <c r="AN9" s="9"/>
       <c r="AO9" s="9"/>
@@ -2753,66 +3052,66 @@
       <c r="BD9" s="9"/>
       <c r="BE9" s="9"/>
       <c r="BF9" s="9"/>
-      <c r="BG9" s="81" t="s">
+      <c r="BG9" s="186" t="s">
         <v>7</v>
       </c>
-      <c r="BH9" s="81"/>
-      <c r="BI9" s="81"/>
-      <c r="BJ9" s="81"/>
-      <c r="BK9" s="81"/>
-      <c r="BL9" s="81"/>
-      <c r="BM9" s="81"/>
-      <c r="BN9" s="81"/>
-      <c r="BO9" s="81"/>
-      <c r="BP9" s="81"/>
+      <c r="BH9" s="186"/>
+      <c r="BI9" s="186"/>
+      <c r="BJ9" s="186"/>
+      <c r="BK9" s="186"/>
+      <c r="BL9" s="186"/>
+      <c r="BM9" s="186"/>
+      <c r="BN9" s="186"/>
+      <c r="BO9" s="186"/>
+      <c r="BP9" s="186"/>
       <c r="BQ9" s="9"/>
       <c r="BR9" s="9"/>
       <c r="BS9" s="9"/>
       <c r="BT9" s="10"/>
-      <c r="BU9" s="37"/>
+      <c r="BU9" s="35"/>
     </row>
     <row r="10" spans="1:73" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="39"/>
-      <c r="B10" s="109" t="s">
-        <v>102</v>
-      </c>
-      <c r="C10" s="110"/>
-      <c r="D10" s="110"/>
-      <c r="E10" s="111"/>
-      <c r="F10" s="45" t="s">
+      <c r="A10" s="37"/>
+      <c r="B10" s="147" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="148"/>
+      <c r="D10" s="148"/>
+      <c r="E10" s="149"/>
+      <c r="F10" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="H10" s="70"/>
-      <c r="I10" s="144"/>
-      <c r="J10" s="58"/>
-      <c r="K10" s="58"/>
-      <c r="L10" s="58"/>
-      <c r="M10" s="58"/>
-      <c r="N10" s="58"/>
-      <c r="O10" s="58"/>
-      <c r="P10" s="58"/>
-      <c r="Q10" s="58"/>
-      <c r="R10" s="58"/>
-      <c r="S10" s="58"/>
-      <c r="T10" s="58"/>
-      <c r="U10" s="58"/>
-      <c r="V10" s="58"/>
-      <c r="W10" s="58"/>
-      <c r="X10" s="58"/>
-      <c r="Y10" s="58"/>
-      <c r="Z10" s="58"/>
-      <c r="AA10" s="58"/>
-      <c r="AB10" s="58"/>
-      <c r="AC10" s="58"/>
-      <c r="AD10" s="58"/>
-      <c r="AE10" s="58"/>
-      <c r="AF10" s="58"/>
-      <c r="AG10" s="58"/>
-      <c r="AH10" s="58"/>
-      <c r="AI10" s="58"/>
-      <c r="AJ10" s="58"/>
-      <c r="AK10" s="58"/>
-      <c r="AL10" s="58"/>
+      <c r="H10" s="124"/>
+      <c r="I10" s="125"/>
+      <c r="J10" s="128"/>
+      <c r="K10" s="128"/>
+      <c r="L10" s="128"/>
+      <c r="M10" s="128"/>
+      <c r="N10" s="128"/>
+      <c r="O10" s="128"/>
+      <c r="P10" s="128"/>
+      <c r="Q10" s="128"/>
+      <c r="R10" s="128"/>
+      <c r="S10" s="128"/>
+      <c r="T10" s="128"/>
+      <c r="U10" s="128"/>
+      <c r="V10" s="128"/>
+      <c r="W10" s="128"/>
+      <c r="X10" s="128"/>
+      <c r="Y10" s="128"/>
+      <c r="Z10" s="128"/>
+      <c r="AA10" s="128"/>
+      <c r="AB10" s="128"/>
+      <c r="AC10" s="128"/>
+      <c r="AD10" s="128"/>
+      <c r="AE10" s="128"/>
+      <c r="AF10" s="128"/>
+      <c r="AG10" s="128"/>
+      <c r="AH10" s="128"/>
+      <c r="AI10" s="128"/>
+      <c r="AJ10" s="128"/>
+      <c r="AK10" s="128"/>
+      <c r="AL10" s="128"/>
       <c r="AM10" s="7"/>
       <c r="AN10" s="7"/>
       <c r="AO10" s="7"/>
@@ -2823,8 +3122,8 @@
       <c r="AT10" s="7"/>
       <c r="AU10" s="7"/>
       <c r="AV10" s="7"/>
-      <c r="AW10" s="52"/>
-      <c r="AX10" s="52"/>
+      <c r="AW10" s="50"/>
+      <c r="AX10" s="50"/>
       <c r="AY10" s="7"/>
       <c r="AZ10" s="7"/>
       <c r="BA10" s="7"/>
@@ -2833,1426 +3132,1426 @@
       <c r="BD10" s="7"/>
       <c r="BE10" s="7"/>
       <c r="BF10" s="7"/>
-      <c r="BG10" s="82"/>
-      <c r="BH10" s="82"/>
-      <c r="BI10" s="82"/>
-      <c r="BJ10" s="82"/>
-      <c r="BK10" s="82"/>
-      <c r="BL10" s="82"/>
-      <c r="BM10" s="82"/>
-      <c r="BN10" s="82"/>
-      <c r="BO10" s="82"/>
-      <c r="BP10" s="82"/>
+      <c r="BG10" s="187"/>
+      <c r="BH10" s="187"/>
+      <c r="BI10" s="187"/>
+      <c r="BJ10" s="187"/>
+      <c r="BK10" s="187"/>
+      <c r="BL10" s="187"/>
+      <c r="BM10" s="187"/>
+      <c r="BN10" s="187"/>
+      <c r="BO10" s="187"/>
+      <c r="BP10" s="187"/>
       <c r="BQ10" s="7"/>
       <c r="BR10" s="7"/>
       <c r="BS10" s="7"/>
       <c r="BT10" s="8"/>
-      <c r="BU10" s="37"/>
+      <c r="BU10" s="35"/>
     </row>
     <row r="11" spans="1:73" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="39"/>
-      <c r="B11" s="109"/>
-      <c r="C11" s="110"/>
-      <c r="D11" s="110"/>
-      <c r="E11" s="111"/>
-      <c r="F11" s="45" t="s">
+      <c r="A11" s="37"/>
+      <c r="B11" s="147" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="148"/>
+      <c r="D11" s="148"/>
+      <c r="E11" s="149"/>
+      <c r="F11" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="H11" s="70"/>
-      <c r="I11" s="71"/>
-      <c r="Y11" s="68" t="s">
+      <c r="H11" s="124"/>
+      <c r="I11" s="126"/>
+      <c r="Y11" s="170" t="s">
         <v>6</v>
       </c>
-      <c r="Z11" s="68"/>
-      <c r="AA11" s="68"/>
-      <c r="AB11" s="68"/>
-      <c r="AC11" s="68"/>
-      <c r="AD11" s="68"/>
-      <c r="AE11" s="68"/>
-      <c r="AF11" s="68"/>
-      <c r="AG11" s="68"/>
-      <c r="AH11" s="68"/>
-      <c r="AI11" s="68"/>
-      <c r="AJ11" s="68"/>
-      <c r="AK11" s="68"/>
-      <c r="AL11" s="68"/>
-      <c r="AM11" s="68"/>
-      <c r="AN11" s="68"/>
-      <c r="AO11" s="68"/>
-      <c r="AP11" s="68"/>
-      <c r="AQ11" s="68"/>
-      <c r="AR11" s="68"/>
-      <c r="AS11" s="68"/>
-      <c r="AT11" s="68"/>
-      <c r="AU11" s="68"/>
-      <c r="AV11" s="16"/>
-      <c r="AW11" s="103"/>
-      <c r="AX11" s="104"/>
-      <c r="AY11" s="16"/>
-      <c r="AZ11" s="68" t="s">
+      <c r="Z11" s="170"/>
+      <c r="AA11" s="170"/>
+      <c r="AB11" s="170"/>
+      <c r="AC11" s="170"/>
+      <c r="AD11" s="170"/>
+      <c r="AE11" s="170"/>
+      <c r="AF11" s="170"/>
+      <c r="AG11" s="170"/>
+      <c r="AH11" s="170"/>
+      <c r="AI11" s="170"/>
+      <c r="AJ11" s="170"/>
+      <c r="AK11" s="170"/>
+      <c r="AL11" s="170"/>
+      <c r="AM11" s="170"/>
+      <c r="AN11" s="170"/>
+      <c r="AO11" s="170"/>
+      <c r="AP11" s="170"/>
+      <c r="AQ11" s="170"/>
+      <c r="AR11" s="170"/>
+      <c r="AS11" s="170"/>
+      <c r="AT11" s="170"/>
+      <c r="AU11" s="170"/>
+      <c r="AV11" s="15"/>
+      <c r="AW11" s="110"/>
+      <c r="AX11" s="123"/>
+      <c r="AY11" s="15"/>
+      <c r="AZ11" s="170" t="s">
         <v>1</v>
       </c>
-      <c r="BA11" s="68"/>
-      <c r="BB11" s="68"/>
-      <c r="BC11" s="68"/>
-      <c r="BD11" s="68"/>
-      <c r="BE11" s="68"/>
-      <c r="BF11" s="68"/>
-      <c r="BG11" s="68"/>
-      <c r="BH11" s="68"/>
-      <c r="BI11" s="68"/>
-      <c r="BJ11" s="68"/>
-      <c r="BK11" s="68"/>
-      <c r="BL11" s="68"/>
-      <c r="BM11" s="68"/>
-      <c r="BN11" s="68"/>
-      <c r="BO11" s="68"/>
-      <c r="BP11" s="68"/>
-      <c r="BQ11" s="68"/>
-      <c r="BR11" s="68"/>
-      <c r="BS11" s="68"/>
+      <c r="BA11" s="170"/>
+      <c r="BB11" s="170"/>
+      <c r="BC11" s="170"/>
+      <c r="BD11" s="170"/>
+      <c r="BE11" s="170"/>
+      <c r="BF11" s="170"/>
+      <c r="BG11" s="170"/>
+      <c r="BH11" s="170"/>
+      <c r="BI11" s="170"/>
+      <c r="BJ11" s="170"/>
+      <c r="BK11" s="170"/>
+      <c r="BL11" s="170"/>
+      <c r="BM11" s="170"/>
+      <c r="BN11" s="170"/>
+      <c r="BO11" s="170"/>
+      <c r="BP11" s="170"/>
+      <c r="BQ11" s="170"/>
+      <c r="BR11" s="170"/>
+      <c r="BS11" s="170"/>
       <c r="BT11" s="4"/>
-      <c r="BU11" s="37"/>
+      <c r="BU11" s="35"/>
     </row>
     <row r="12" spans="1:73" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="39"/>
-      <c r="B12" s="109"/>
-      <c r="C12" s="110"/>
-      <c r="D12" s="110"/>
-      <c r="E12" s="111"/>
-      <c r="F12" s="45" t="s">
+      <c r="A12" s="37"/>
+      <c r="B12" s="147"/>
+      <c r="C12" s="148"/>
+      <c r="D12" s="148"/>
+      <c r="E12" s="149"/>
+      <c r="F12" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="H12" s="70"/>
-      <c r="I12" s="71"/>
-      <c r="X12" s="24">
+      <c r="H12" s="124"/>
+      <c r="I12" s="126"/>
+      <c r="X12" s="23">
         <v>23</v>
       </c>
-      <c r="Y12" s="25">
+      <c r="Y12" s="24">
         <v>22</v>
       </c>
-      <c r="Z12" s="26">
+      <c r="Z12" s="25">
         <v>21</v>
       </c>
-      <c r="AA12" s="26">
+      <c r="AA12" s="25">
         <v>20</v>
       </c>
-      <c r="AB12" s="26">
+      <c r="AB12" s="25">
         <v>19</v>
       </c>
-      <c r="AC12" s="26">
+      <c r="AC12" s="25">
         <v>18</v>
       </c>
-      <c r="AD12" s="26">
+      <c r="AD12" s="25">
         <v>17</v>
       </c>
-      <c r="AE12" s="26">
+      <c r="AE12" s="25">
         <v>16</v>
       </c>
-      <c r="AF12" s="26">
+      <c r="AF12" s="25">
         <v>15</v>
       </c>
-      <c r="AG12" s="26">
+      <c r="AG12" s="25">
         <v>14</v>
       </c>
-      <c r="AH12" s="26">
+      <c r="AH12" s="25">
         <v>13</v>
       </c>
-      <c r="AI12" s="155" t="s">
+      <c r="AI12" s="118" t="s">
         <v>11</v>
       </c>
-      <c r="AJ12" s="26">
+      <c r="AJ12" s="25">
         <v>12</v>
       </c>
-      <c r="AK12" s="26">
+      <c r="AK12" s="25">
         <v>11</v>
       </c>
-      <c r="AL12" s="26">
+      <c r="AL12" s="25">
         <v>10</v>
       </c>
-      <c r="AM12" s="26">
+      <c r="AM12" s="25">
         <v>9</v>
       </c>
-      <c r="AN12" s="26">
+      <c r="AN12" s="25">
         <v>8</v>
       </c>
-      <c r="AO12" s="27">
+      <c r="AO12" s="26">
         <v>7</v>
       </c>
-      <c r="AP12" s="26">
+      <c r="AP12" s="25">
         <v>6</v>
       </c>
-      <c r="AQ12" s="26">
+      <c r="AQ12" s="25">
         <v>5</v>
       </c>
-      <c r="AR12" s="26">
+      <c r="AR12" s="25">
         <v>4</v>
       </c>
-      <c r="AS12" s="26">
+      <c r="AS12" s="25">
         <v>3</v>
       </c>
-      <c r="AT12" s="28">
+      <c r="AT12" s="27">
         <v>2</v>
       </c>
-      <c r="AU12" s="72" t="s">
+      <c r="AU12" s="183" t="s">
         <v>11</v>
       </c>
-      <c r="AW12" s="103"/>
-      <c r="AX12" s="104"/>
-      <c r="AZ12" s="47">
+      <c r="AW12" s="110"/>
+      <c r="AX12" s="123"/>
+      <c r="AZ12" s="45">
         <v>1</v>
       </c>
-      <c r="BA12" s="42">
+      <c r="BA12" s="40">
         <v>2</v>
       </c>
-      <c r="BB12" s="42">
+      <c r="BB12" s="40">
         <v>3</v>
       </c>
-      <c r="BC12" s="42">
+      <c r="BC12" s="40">
         <v>4</v>
       </c>
-      <c r="BD12" s="42">
+      <c r="BD12" s="40">
         <v>5</v>
       </c>
-      <c r="BE12" s="42">
+      <c r="BE12" s="40">
         <v>6</v>
       </c>
-      <c r="BF12" s="42">
+      <c r="BF12" s="40">
         <v>7</v>
       </c>
-      <c r="BG12" s="42">
+      <c r="BG12" s="40">
         <v>8</v>
       </c>
-      <c r="BH12" s="72" t="s">
+      <c r="BH12" s="183" t="s">
         <v>11</v>
       </c>
-      <c r="BI12" s="26">
+      <c r="BI12" s="25">
         <v>9</v>
       </c>
-      <c r="BJ12" s="28">
+      <c r="BJ12" s="27">
         <v>10</v>
       </c>
-      <c r="BK12" s="28">
+      <c r="BK12" s="27">
         <v>11</v>
       </c>
-      <c r="BL12" s="25">
+      <c r="BL12" s="24">
         <v>12</v>
       </c>
-      <c r="BM12" s="26">
+      <c r="BM12" s="25">
         <v>13</v>
       </c>
-      <c r="BN12" s="26">
+      <c r="BN12" s="25">
         <v>14</v>
       </c>
-      <c r="BO12" s="26">
+      <c r="BO12" s="25">
         <v>15</v>
       </c>
-      <c r="BP12" s="26">
+      <c r="BP12" s="25">
         <v>16</v>
       </c>
-      <c r="BQ12" s="26">
+      <c r="BQ12" s="25">
         <v>17</v>
       </c>
-      <c r="BR12" s="26">
+      <c r="BR12" s="25">
         <v>18</v>
       </c>
-      <c r="BS12" s="28">
+      <c r="BS12" s="27">
         <v>19</v>
       </c>
       <c r="BT12" s="4"/>
-      <c r="BU12" s="37"/>
+      <c r="BU12" s="35"/>
     </row>
     <row r="13" spans="1:73" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="39"/>
-      <c r="B13" s="109" t="s">
-        <v>103</v>
-      </c>
-      <c r="C13" s="110"/>
-      <c r="D13" s="110"/>
-      <c r="E13" s="111"/>
-      <c r="F13" s="45" t="s">
+      <c r="A13" s="37"/>
+      <c r="B13" s="147" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="148"/>
+      <c r="D13" s="148"/>
+      <c r="E13" s="149"/>
+      <c r="F13" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="H13" s="70"/>
-      <c r="I13" s="71"/>
-      <c r="X13" s="59" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y13" s="62" t="s">
-        <v>71</v>
-      </c>
-      <c r="Z13" s="62" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA13" s="62" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB13" s="62" t="s">
-        <v>53</v>
-      </c>
-      <c r="AC13" s="62" t="s">
-        <v>90</v>
-      </c>
-      <c r="AD13" s="62" t="s">
-        <v>90</v>
-      </c>
-      <c r="AE13" s="62" t="s">
-        <v>90</v>
-      </c>
-      <c r="AF13" s="62" t="s">
-        <v>77</v>
-      </c>
-      <c r="AG13" s="62" t="s">
+      <c r="H13" s="124"/>
+      <c r="I13" s="126"/>
+      <c r="X13" s="153" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y13" s="103" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z13" s="103" t="s">
+        <v>101</v>
+      </c>
+      <c r="AA13" s="103" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB13" s="103"/>
+      <c r="AC13" s="103" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD13" s="103" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE13" s="103" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF13" s="103" t="s">
+        <v>106</v>
+      </c>
+      <c r="AG13" s="103" t="s">
         <v>109</v>
       </c>
-      <c r="AH13" s="62" t="s">
+      <c r="AH13" s="103" t="s">
+        <v>109</v>
+      </c>
+      <c r="AI13" s="119"/>
+      <c r="AJ13" s="103" t="s">
+        <v>106</v>
+      </c>
+      <c r="AK13" s="103"/>
+      <c r="AL13" s="103"/>
+      <c r="AM13" s="103"/>
+      <c r="AN13" s="103"/>
+      <c r="AO13" s="103" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP13" s="103" t="s">
+        <v>93</v>
+      </c>
+      <c r="AQ13" s="103"/>
+      <c r="AR13" s="103" t="s">
+        <v>94</v>
+      </c>
+      <c r="AS13" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="AI13" s="156"/>
-      <c r="AJ13" s="62" t="s">
+      <c r="AT13" s="115" t="s">
         <v>51</v>
       </c>
-      <c r="AK13" s="62" t="s">
-        <v>54</v>
-      </c>
-      <c r="AL13" s="62" t="s">
-        <v>54</v>
-      </c>
-      <c r="AM13" s="62" t="s">
+      <c r="AU13" s="184"/>
+      <c r="AW13" s="110"/>
+      <c r="AX13" s="123"/>
+      <c r="AY13" s="195"/>
+      <c r="AZ13" s="153" t="s">
+        <v>74</v>
+      </c>
+      <c r="BA13" s="103" t="s">
+        <v>106</v>
+      </c>
+      <c r="BB13" s="103" t="s">
+        <v>106</v>
+      </c>
+      <c r="BC13" s="103"/>
+      <c r="BD13" s="103" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE13" s="103" t="s">
+        <v>100</v>
+      </c>
+      <c r="BF13" s="103" t="s">
         <v>108</v>
       </c>
-      <c r="AN13" s="62" t="s">
+      <c r="BG13" s="103" t="s">
         <v>108</v>
       </c>
-      <c r="AO13" s="62" t="s">
-        <v>107</v>
-      </c>
-      <c r="AP13" s="62" t="s">
-        <v>107</v>
-      </c>
-      <c r="AQ13" s="62" t="s">
-        <v>96</v>
-      </c>
-      <c r="AR13" s="62" t="s">
-        <v>96</v>
-      </c>
-      <c r="AS13" s="62"/>
-      <c r="AT13" s="76" t="s">
-        <v>99</v>
-      </c>
-      <c r="AU13" s="73"/>
-      <c r="AW13" s="103"/>
-      <c r="AX13" s="104"/>
-      <c r="AY13" s="75"/>
-      <c r="AZ13" s="59" t="s">
-        <v>69</v>
-      </c>
-      <c r="BA13" s="62" t="s">
-        <v>90</v>
-      </c>
-      <c r="BB13" s="62" t="s">
-        <v>90</v>
-      </c>
-      <c r="BC13" s="62" t="s">
-        <v>93</v>
-      </c>
-      <c r="BD13" s="62" t="s">
-        <v>93</v>
-      </c>
-      <c r="BE13" s="62" t="s">
-        <v>92</v>
-      </c>
-      <c r="BF13" s="62" t="s">
-        <v>92</v>
-      </c>
-      <c r="BG13" s="62" t="s">
-        <v>92</v>
-      </c>
-      <c r="BH13" s="84"/>
-      <c r="BI13" s="145" t="s">
-        <v>88</v>
-      </c>
-      <c r="BJ13" s="78" t="s">
-        <v>88</v>
-      </c>
-      <c r="BK13" s="78"/>
-      <c r="BL13" s="78"/>
-      <c r="BM13" s="78"/>
-      <c r="BN13" s="78"/>
-      <c r="BO13" s="78" t="s">
-        <v>106</v>
-      </c>
-      <c r="BP13" s="78"/>
-      <c r="BQ13" s="78"/>
-      <c r="BR13" s="78"/>
-      <c r="BS13" s="152"/>
+      <c r="BH13" s="188"/>
+      <c r="BI13" s="106"/>
+      <c r="BJ13" s="107"/>
+      <c r="BK13" s="107"/>
+      <c r="BL13" s="107"/>
+      <c r="BM13" s="107"/>
+      <c r="BN13" s="107" t="s">
+        <v>113</v>
+      </c>
+      <c r="BO13" s="107" t="s">
+        <v>113</v>
+      </c>
+      <c r="BP13" s="107" t="s">
+        <v>113</v>
+      </c>
+      <c r="BQ13" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="BR13" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="BS13" s="112"/>
       <c r="BT13" s="4"/>
-      <c r="BU13" s="37"/>
+      <c r="BU13" s="35"/>
     </row>
     <row r="14" spans="1:73" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="39"/>
-      <c r="B14" s="109" t="s">
-        <v>103</v>
-      </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="110"/>
-      <c r="E14" s="111"/>
-      <c r="F14" s="45" t="s">
+      <c r="A14" s="37"/>
+      <c r="B14" s="147"/>
+      <c r="C14" s="148"/>
+      <c r="D14" s="148"/>
+      <c r="E14" s="149"/>
+      <c r="F14" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="H14" s="70"/>
-      <c r="I14" s="71"/>
-      <c r="X14" s="60"/>
-      <c r="Y14" s="63"/>
-      <c r="Z14" s="63"/>
-      <c r="AA14" s="63"/>
-      <c r="AB14" s="63"/>
-      <c r="AC14" s="63"/>
-      <c r="AD14" s="63"/>
-      <c r="AE14" s="63"/>
-      <c r="AF14" s="63"/>
-      <c r="AG14" s="63"/>
-      <c r="AH14" s="63"/>
-      <c r="AI14" s="156"/>
-      <c r="AJ14" s="63"/>
-      <c r="AK14" s="63"/>
-      <c r="AL14" s="63"/>
-      <c r="AM14" s="63"/>
-      <c r="AN14" s="63"/>
-      <c r="AO14" s="63"/>
-      <c r="AP14" s="63"/>
-      <c r="AQ14" s="63"/>
-      <c r="AR14" s="63"/>
-      <c r="AS14" s="63"/>
-      <c r="AT14" s="77"/>
-      <c r="AU14" s="73"/>
-      <c r="AW14" s="70" t="s">
+      <c r="H14" s="124"/>
+      <c r="I14" s="126"/>
+      <c r="X14" s="154"/>
+      <c r="Y14" s="104"/>
+      <c r="Z14" s="104"/>
+      <c r="AA14" s="104"/>
+      <c r="AB14" s="104"/>
+      <c r="AC14" s="104"/>
+      <c r="AD14" s="104"/>
+      <c r="AE14" s="104"/>
+      <c r="AF14" s="104"/>
+      <c r="AG14" s="104"/>
+      <c r="AH14" s="104"/>
+      <c r="AI14" s="119"/>
+      <c r="AJ14" s="104"/>
+      <c r="AK14" s="104"/>
+      <c r="AL14" s="104"/>
+      <c r="AM14" s="104"/>
+      <c r="AN14" s="104"/>
+      <c r="AO14" s="104"/>
+      <c r="AP14" s="104"/>
+      <c r="AQ14" s="104"/>
+      <c r="AR14" s="104"/>
+      <c r="AS14" s="104"/>
+      <c r="AT14" s="116"/>
+      <c r="AU14" s="184"/>
+      <c r="AW14" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="AX14" s="71"/>
-      <c r="AY14" s="75"/>
-      <c r="AZ14" s="60"/>
-      <c r="BA14" s="63"/>
-      <c r="BB14" s="63"/>
-      <c r="BC14" s="63"/>
-      <c r="BD14" s="63"/>
-      <c r="BE14" s="63"/>
-      <c r="BF14" s="63"/>
-      <c r="BG14" s="63"/>
-      <c r="BH14" s="84"/>
-      <c r="BI14" s="146"/>
-      <c r="BJ14" s="79"/>
-      <c r="BK14" s="79"/>
-      <c r="BL14" s="79"/>
-      <c r="BM14" s="79"/>
-      <c r="BN14" s="79"/>
-      <c r="BO14" s="79"/>
-      <c r="BP14" s="79"/>
-      <c r="BQ14" s="79"/>
-      <c r="BR14" s="79"/>
-      <c r="BS14" s="153"/>
+      <c r="AX14" s="126"/>
+      <c r="AY14" s="195"/>
+      <c r="AZ14" s="154"/>
+      <c r="BA14" s="104"/>
+      <c r="BB14" s="104"/>
+      <c r="BC14" s="104"/>
+      <c r="BD14" s="104"/>
+      <c r="BE14" s="104"/>
+      <c r="BF14" s="104"/>
+      <c r="BG14" s="104"/>
+      <c r="BH14" s="188"/>
+      <c r="BI14" s="101"/>
+      <c r="BJ14" s="95"/>
+      <c r="BK14" s="95"/>
+      <c r="BL14" s="95"/>
+      <c r="BM14" s="95"/>
+      <c r="BN14" s="95"/>
+      <c r="BO14" s="95"/>
+      <c r="BP14" s="95"/>
+      <c r="BQ14" s="95"/>
+      <c r="BR14" s="95"/>
+      <c r="BS14" s="113"/>
       <c r="BT14" s="4"/>
-      <c r="BU14" s="37"/>
+      <c r="BU14" s="35"/>
     </row>
     <row r="15" spans="1:73" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="39"/>
-      <c r="B15" s="109" t="s">
-        <v>103</v>
-      </c>
-      <c r="C15" s="110"/>
-      <c r="D15" s="110"/>
-      <c r="E15" s="111"/>
-      <c r="F15" s="45" t="s">
+      <c r="A15" s="37"/>
+      <c r="B15" s="147" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="148"/>
+      <c r="D15" s="148"/>
+      <c r="E15" s="149"/>
+      <c r="F15" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="70"/>
-      <c r="I15" s="71"/>
-      <c r="X15" s="60"/>
-      <c r="Y15" s="63"/>
-      <c r="Z15" s="63"/>
-      <c r="AA15" s="63"/>
-      <c r="AB15" s="63"/>
-      <c r="AC15" s="63"/>
-      <c r="AD15" s="63"/>
-      <c r="AE15" s="63"/>
-      <c r="AF15" s="63"/>
-      <c r="AG15" s="63"/>
-      <c r="AH15" s="63"/>
-      <c r="AI15" s="156"/>
-      <c r="AJ15" s="63"/>
-      <c r="AK15" s="63"/>
-      <c r="AL15" s="63"/>
-      <c r="AM15" s="63"/>
-      <c r="AN15" s="63"/>
-      <c r="AO15" s="63"/>
-      <c r="AP15" s="63"/>
-      <c r="AQ15" s="63"/>
-      <c r="AR15" s="63"/>
-      <c r="AS15" s="63"/>
-      <c r="AT15" s="77"/>
-      <c r="AU15" s="73"/>
-      <c r="AW15" s="70"/>
-      <c r="AX15" s="71"/>
-      <c r="AY15" s="75"/>
-      <c r="AZ15" s="60"/>
-      <c r="BA15" s="63"/>
-      <c r="BB15" s="63"/>
-      <c r="BC15" s="63"/>
-      <c r="BD15" s="63"/>
-      <c r="BE15" s="63"/>
-      <c r="BF15" s="63"/>
-      <c r="BG15" s="63"/>
-      <c r="BH15" s="84"/>
-      <c r="BI15" s="146"/>
-      <c r="BJ15" s="79"/>
-      <c r="BK15" s="79"/>
-      <c r="BL15" s="79"/>
-      <c r="BM15" s="79"/>
-      <c r="BN15" s="79"/>
-      <c r="BO15" s="79"/>
-      <c r="BP15" s="79"/>
-      <c r="BQ15" s="79"/>
-      <c r="BR15" s="79"/>
-      <c r="BS15" s="153"/>
+      <c r="H15" s="124"/>
+      <c r="I15" s="126"/>
+      <c r="X15" s="154"/>
+      <c r="Y15" s="104"/>
+      <c r="Z15" s="104"/>
+      <c r="AA15" s="104"/>
+      <c r="AB15" s="104"/>
+      <c r="AC15" s="104"/>
+      <c r="AD15" s="104"/>
+      <c r="AE15" s="104"/>
+      <c r="AF15" s="104"/>
+      <c r="AG15" s="104"/>
+      <c r="AH15" s="104"/>
+      <c r="AI15" s="119"/>
+      <c r="AJ15" s="104"/>
+      <c r="AK15" s="104"/>
+      <c r="AL15" s="104"/>
+      <c r="AM15" s="104"/>
+      <c r="AN15" s="104"/>
+      <c r="AO15" s="104"/>
+      <c r="AP15" s="104"/>
+      <c r="AQ15" s="104"/>
+      <c r="AR15" s="104"/>
+      <c r="AS15" s="104"/>
+      <c r="AT15" s="116"/>
+      <c r="AU15" s="184"/>
+      <c r="AW15" s="124"/>
+      <c r="AX15" s="126"/>
+      <c r="AY15" s="195"/>
+      <c r="AZ15" s="154"/>
+      <c r="BA15" s="104"/>
+      <c r="BB15" s="104"/>
+      <c r="BC15" s="104"/>
+      <c r="BD15" s="104"/>
+      <c r="BE15" s="104"/>
+      <c r="BF15" s="104"/>
+      <c r="BG15" s="104"/>
+      <c r="BH15" s="188"/>
+      <c r="BI15" s="101"/>
+      <c r="BJ15" s="95"/>
+      <c r="BK15" s="95"/>
+      <c r="BL15" s="95"/>
+      <c r="BM15" s="95"/>
+      <c r="BN15" s="95"/>
+      <c r="BO15" s="95"/>
+      <c r="BP15" s="95"/>
+      <c r="BQ15" s="95"/>
+      <c r="BR15" s="95"/>
+      <c r="BS15" s="113"/>
       <c r="BT15" s="4"/>
-      <c r="BU15" s="37"/>
+      <c r="BU15" s="35"/>
     </row>
     <row r="16" spans="1:73" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="39"/>
-      <c r="B16" s="109" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" s="110"/>
-      <c r="D16" s="110"/>
-      <c r="E16" s="111"/>
-      <c r="F16" s="45" t="s">
+      <c r="A16" s="37"/>
+      <c r="B16" s="147"/>
+      <c r="C16" s="148"/>
+      <c r="D16" s="148"/>
+      <c r="E16" s="149"/>
+      <c r="F16" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="H16" s="70"/>
-      <c r="I16" s="71"/>
-      <c r="X16" s="61"/>
-      <c r="Y16" s="67"/>
-      <c r="Z16" s="67"/>
-      <c r="AA16" s="67"/>
-      <c r="AB16" s="67"/>
-      <c r="AC16" s="67"/>
-      <c r="AD16" s="67"/>
-      <c r="AE16" s="67"/>
-      <c r="AF16" s="67"/>
-      <c r="AG16" s="67"/>
-      <c r="AH16" s="67"/>
-      <c r="AI16" s="157"/>
-      <c r="AJ16" s="67"/>
-      <c r="AK16" s="67"/>
-      <c r="AL16" s="67"/>
-      <c r="AM16" s="67"/>
-      <c r="AN16" s="67"/>
-      <c r="AO16" s="67"/>
-      <c r="AP16" s="67"/>
-      <c r="AQ16" s="67"/>
-      <c r="AR16" s="67"/>
-      <c r="AS16" s="67"/>
-      <c r="AT16" s="105"/>
-      <c r="AU16" s="74"/>
-      <c r="AW16" s="70"/>
-      <c r="AX16" s="71"/>
-      <c r="AY16" s="75"/>
-      <c r="AZ16" s="61"/>
-      <c r="BA16" s="67"/>
-      <c r="BB16" s="67"/>
-      <c r="BC16" s="67"/>
-      <c r="BD16" s="67"/>
-      <c r="BE16" s="67"/>
-      <c r="BF16" s="67"/>
-      <c r="BG16" s="67"/>
-      <c r="BH16" s="85"/>
-      <c r="BI16" s="147"/>
-      <c r="BJ16" s="80"/>
-      <c r="BK16" s="80"/>
-      <c r="BL16" s="80"/>
-      <c r="BM16" s="80"/>
-      <c r="BN16" s="80"/>
-      <c r="BO16" s="80"/>
-      <c r="BP16" s="80"/>
-      <c r="BQ16" s="80"/>
-      <c r="BR16" s="80"/>
-      <c r="BS16" s="154"/>
+      <c r="H16" s="124"/>
+      <c r="I16" s="126"/>
+      <c r="X16" s="155"/>
+      <c r="Y16" s="105"/>
+      <c r="Z16" s="105"/>
+      <c r="AA16" s="105"/>
+      <c r="AB16" s="105"/>
+      <c r="AC16" s="105"/>
+      <c r="AD16" s="105"/>
+      <c r="AE16" s="105"/>
+      <c r="AF16" s="105"/>
+      <c r="AG16" s="105"/>
+      <c r="AH16" s="105"/>
+      <c r="AI16" s="120"/>
+      <c r="AJ16" s="105"/>
+      <c r="AK16" s="105"/>
+      <c r="AL16" s="105"/>
+      <c r="AM16" s="105"/>
+      <c r="AN16" s="105"/>
+      <c r="AO16" s="105"/>
+      <c r="AP16" s="105"/>
+      <c r="AQ16" s="105"/>
+      <c r="AR16" s="105"/>
+      <c r="AS16" s="105"/>
+      <c r="AT16" s="117"/>
+      <c r="AU16" s="185"/>
+      <c r="AW16" s="124"/>
+      <c r="AX16" s="126"/>
+      <c r="AY16" s="195"/>
+      <c r="AZ16" s="155"/>
+      <c r="BA16" s="105"/>
+      <c r="BB16" s="105"/>
+      <c r="BC16" s="105"/>
+      <c r="BD16" s="105"/>
+      <c r="BE16" s="105"/>
+      <c r="BF16" s="105"/>
+      <c r="BG16" s="105"/>
+      <c r="BH16" s="189"/>
+      <c r="BI16" s="102"/>
+      <c r="BJ16" s="96"/>
+      <c r="BK16" s="96"/>
+      <c r="BL16" s="96"/>
+      <c r="BM16" s="96"/>
+      <c r="BN16" s="96"/>
+      <c r="BO16" s="96"/>
+      <c r="BP16" s="96"/>
+      <c r="BQ16" s="96"/>
+      <c r="BR16" s="96"/>
+      <c r="BS16" s="114"/>
       <c r="BT16" s="4"/>
-      <c r="BU16" s="37"/>
+      <c r="BU16" s="35"/>
     </row>
     <row r="17" spans="1:73" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="39"/>
-      <c r="B17" s="109"/>
-      <c r="C17" s="110"/>
-      <c r="D17" s="110"/>
-      <c r="E17" s="111"/>
-      <c r="F17" s="45" t="s">
+      <c r="A17" s="37"/>
+      <c r="B17" s="147" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="148"/>
+      <c r="D17" s="148"/>
+      <c r="E17" s="149"/>
+      <c r="F17" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="H17" s="70"/>
-      <c r="I17" s="71"/>
-      <c r="AW17" s="70"/>
-      <c r="AX17" s="71"/>
+      <c r="H17" s="124"/>
+      <c r="I17" s="126"/>
+      <c r="AW17" s="124"/>
+      <c r="AX17" s="126"/>
       <c r="BT17" s="4"/>
-      <c r="BU17" s="37"/>
+      <c r="BU17" s="35"/>
     </row>
     <row r="18" spans="1:73" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="39"/>
-      <c r="B18" s="109"/>
-      <c r="C18" s="110"/>
-      <c r="D18" s="110"/>
-      <c r="E18" s="111"/>
-      <c r="F18" s="45" t="s">
+      <c r="A18" s="37"/>
+      <c r="B18" s="147"/>
+      <c r="C18" s="148"/>
+      <c r="D18" s="148"/>
+      <c r="E18" s="149"/>
+      <c r="F18" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="H18" s="70"/>
-      <c r="I18" s="71"/>
-      <c r="K18" s="119"/>
-      <c r="L18" s="116"/>
-      <c r="M18" s="134"/>
-      <c r="N18" s="78"/>
-      <c r="O18" s="78"/>
-      <c r="P18" s="78"/>
-      <c r="Q18" s="78"/>
-      <c r="R18" s="78"/>
-      <c r="S18" s="78"/>
-      <c r="T18" s="78"/>
-      <c r="U18" s="78" t="s">
-        <v>95</v>
-      </c>
-      <c r="V18" s="78" t="s">
-        <v>95</v>
-      </c>
-      <c r="W18" s="78" t="s">
-        <v>60</v>
-      </c>
-      <c r="X18" s="78" t="s">
+      <c r="H18" s="124"/>
+      <c r="I18" s="126"/>
+      <c r="K18" s="159"/>
+      <c r="L18" s="156"/>
+      <c r="M18" s="136"/>
+      <c r="N18" s="107"/>
+      <c r="O18" s="107"/>
+      <c r="P18" s="107"/>
+      <c r="Q18" s="107"/>
+      <c r="R18" s="107"/>
+      <c r="S18" s="107"/>
+      <c r="T18" s="107"/>
+      <c r="U18" s="107"/>
+      <c r="V18" s="107" t="s">
+        <v>104</v>
+      </c>
+      <c r="W18" s="107" t="s">
+        <v>104</v>
+      </c>
+      <c r="X18" s="107"/>
+      <c r="Y18" s="103" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z18" s="103" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA18" s="103" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB18" s="103" t="s">
+        <v>114</v>
+      </c>
+      <c r="AC18" s="103"/>
+      <c r="AD18" s="103"/>
+      <c r="AE18" s="103" t="s">
         <v>63</v>
       </c>
-      <c r="Y18" s="62" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z18" s="62"/>
-      <c r="AA18" s="62" t="s">
+      <c r="AF18" s="103" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG18" s="103" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH18" s="103" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI18" s="103" t="s">
+        <v>52</v>
+      </c>
+      <c r="AJ18" s="103" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK18" s="103" t="s">
+        <v>67</v>
+      </c>
+      <c r="AL18" s="103" t="s">
+        <v>58</v>
+      </c>
+      <c r="AM18" s="103" t="s">
+        <v>57</v>
+      </c>
+      <c r="AN18" s="115" t="s">
+        <v>62</v>
+      </c>
+      <c r="AO18" s="140" t="s">
+        <v>103</v>
+      </c>
+      <c r="AP18" s="103" t="s">
+        <v>103</v>
+      </c>
+      <c r="AQ18" s="103" t="s">
+        <v>103</v>
+      </c>
+      <c r="AR18" s="103" t="s">
         <v>97</v>
       </c>
-      <c r="AB18" s="62" t="s">
+      <c r="AS18" s="103" t="s">
         <v>97</v>
       </c>
-      <c r="AC18" s="62" t="s">
+      <c r="AT18" s="103"/>
+      <c r="AU18" s="115"/>
+      <c r="AW18" s="124"/>
+      <c r="AX18" s="126"/>
+      <c r="AZ18" s="153" t="s">
+        <v>115</v>
+      </c>
+      <c r="BA18" s="103" t="s">
+        <v>115</v>
+      </c>
+      <c r="BB18" s="103"/>
+      <c r="BC18" s="103" t="s">
+        <v>68</v>
+      </c>
+      <c r="BD18" s="103" t="s">
+        <v>68</v>
+      </c>
+      <c r="BE18" s="103" t="s">
+        <v>69</v>
+      </c>
+      <c r="BF18" s="103" t="s">
+        <v>69</v>
+      </c>
+      <c r="BG18" s="103"/>
+      <c r="BH18" s="103"/>
+      <c r="BI18" s="103" t="s">
+        <v>70</v>
+      </c>
+      <c r="BJ18" s="103" t="s">
+        <v>71</v>
+      </c>
+      <c r="BK18" s="103" t="s">
+        <v>54</v>
+      </c>
+      <c r="BL18" s="103" t="s">
+        <v>72</v>
+      </c>
+      <c r="BM18" s="103" t="s">
+        <v>72</v>
+      </c>
+      <c r="BN18" s="103" t="s">
+        <v>111</v>
+      </c>
+      <c r="BO18" s="103" t="s">
+        <v>111</v>
+      </c>
+      <c r="BP18" s="103" t="s">
         <v>104</v>
       </c>
-      <c r="AD18" s="62" t="s">
+      <c r="BQ18" s="103" t="s">
         <v>104</v>
       </c>
-      <c r="AE18" s="62" t="s">
+      <c r="BR18" s="103" t="s">
         <v>104</v>
       </c>
-      <c r="AF18" s="62" t="s">
-        <v>59</v>
-      </c>
-      <c r="AG18" s="62" t="s">
-        <v>61</v>
-      </c>
-      <c r="AH18" s="62" t="s">
-        <v>62</v>
-      </c>
-      <c r="AI18" s="62" t="s">
-        <v>52</v>
-      </c>
-      <c r="AJ18" s="62" t="s">
-        <v>63</v>
-      </c>
-      <c r="AK18" s="62" t="s">
-        <v>64</v>
-      </c>
-      <c r="AL18" s="62"/>
-      <c r="AM18" s="62" t="s">
-        <v>56</v>
-      </c>
-      <c r="AN18" s="76"/>
-      <c r="AO18" s="138" t="s">
-        <v>60</v>
-      </c>
-      <c r="AP18" s="62" t="s">
-        <v>89</v>
-      </c>
-      <c r="AQ18" s="62" t="s">
-        <v>89</v>
-      </c>
-      <c r="AR18" s="62" t="s">
-        <v>85</v>
-      </c>
-      <c r="AS18" s="62"/>
-      <c r="AT18" s="62" t="s">
-        <v>105</v>
-      </c>
-      <c r="AU18" s="76"/>
-      <c r="AW18" s="70"/>
-      <c r="AX18" s="71"/>
-      <c r="AZ18" s="59" t="s">
-        <v>98</v>
-      </c>
-      <c r="BA18" s="62" t="s">
-        <v>98</v>
-      </c>
-      <c r="BB18" s="62"/>
-      <c r="BC18" s="62" t="s">
-        <v>65</v>
-      </c>
-      <c r="BD18" s="62" t="s">
-        <v>65</v>
-      </c>
-      <c r="BE18" s="62" t="s">
-        <v>66</v>
-      </c>
-      <c r="BF18" s="62" t="s">
-        <v>66</v>
-      </c>
-      <c r="BG18" s="62" t="s">
-        <v>67</v>
-      </c>
-      <c r="BH18" s="62" t="s">
-        <v>67</v>
-      </c>
-      <c r="BI18" s="62"/>
-      <c r="BJ18" s="62"/>
-      <c r="BK18" s="62" t="s">
-        <v>95</v>
-      </c>
-      <c r="BL18" s="62" t="s">
-        <v>95</v>
-      </c>
-      <c r="BM18" s="62" t="s">
-        <v>68</v>
-      </c>
-      <c r="BN18" s="62" t="s">
-        <v>68</v>
-      </c>
-      <c r="BO18" s="62"/>
-      <c r="BP18" s="62"/>
-      <c r="BQ18" s="62"/>
-      <c r="BR18" s="62"/>
-      <c r="BS18" s="76"/>
+      <c r="BS18" s="115" t="s">
+        <v>73</v>
+      </c>
       <c r="BT18" s="4"/>
-      <c r="BU18" s="37"/>
+      <c r="BU18" s="35"/>
     </row>
     <row r="19" spans="1:73" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="39"/>
-      <c r="B19" s="112"/>
-      <c r="C19" s="113"/>
-      <c r="D19" s="113"/>
-      <c r="E19" s="114"/>
-      <c r="F19" s="46" t="s">
+      <c r="A19" s="37"/>
+      <c r="B19" s="150"/>
+      <c r="C19" s="151"/>
+      <c r="D19" s="151"/>
+      <c r="E19" s="152"/>
+      <c r="F19" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="H19" s="70"/>
-      <c r="I19" s="71"/>
-      <c r="K19" s="120"/>
-      <c r="L19" s="117"/>
-      <c r="M19" s="135"/>
-      <c r="N19" s="79"/>
-      <c r="O19" s="79"/>
-      <c r="P19" s="79"/>
-      <c r="Q19" s="79"/>
-      <c r="R19" s="79"/>
-      <c r="S19" s="79"/>
-      <c r="T19" s="79"/>
-      <c r="U19" s="79"/>
-      <c r="V19" s="79"/>
-      <c r="W19" s="79"/>
-      <c r="X19" s="79"/>
-      <c r="Y19" s="63"/>
-      <c r="Z19" s="63"/>
-      <c r="AA19" s="63"/>
-      <c r="AB19" s="63"/>
-      <c r="AC19" s="63"/>
-      <c r="AD19" s="63"/>
-      <c r="AE19" s="63"/>
-      <c r="AF19" s="63"/>
-      <c r="AG19" s="63"/>
-      <c r="AH19" s="63"/>
-      <c r="AI19" s="63"/>
-      <c r="AJ19" s="63"/>
-      <c r="AK19" s="63"/>
-      <c r="AL19" s="63"/>
-      <c r="AM19" s="63"/>
-      <c r="AN19" s="77"/>
-      <c r="AO19" s="139"/>
-      <c r="AP19" s="63"/>
-      <c r="AQ19" s="63"/>
-      <c r="AR19" s="63"/>
-      <c r="AS19" s="63"/>
-      <c r="AT19" s="63"/>
-      <c r="AU19" s="77"/>
-      <c r="AW19" s="70"/>
-      <c r="AX19" s="71"/>
-      <c r="AZ19" s="60"/>
-      <c r="BA19" s="63"/>
-      <c r="BB19" s="63"/>
-      <c r="BC19" s="63"/>
-      <c r="BD19" s="63"/>
-      <c r="BE19" s="63"/>
-      <c r="BF19" s="63"/>
-      <c r="BG19" s="63"/>
-      <c r="BH19" s="63"/>
-      <c r="BI19" s="63"/>
-      <c r="BJ19" s="63"/>
-      <c r="BK19" s="63"/>
-      <c r="BL19" s="63"/>
-      <c r="BM19" s="63"/>
-      <c r="BN19" s="63"/>
-      <c r="BO19" s="63"/>
-      <c r="BP19" s="63"/>
-      <c r="BQ19" s="63"/>
-      <c r="BR19" s="63"/>
-      <c r="BS19" s="77"/>
+      <c r="H19" s="124"/>
+      <c r="I19" s="126"/>
+      <c r="K19" s="160"/>
+      <c r="L19" s="157"/>
+      <c r="M19" s="137"/>
+      <c r="N19" s="95"/>
+      <c r="O19" s="95"/>
+      <c r="P19" s="95"/>
+      <c r="Q19" s="95"/>
+      <c r="R19" s="95"/>
+      <c r="S19" s="95"/>
+      <c r="T19" s="95"/>
+      <c r="U19" s="95"/>
+      <c r="V19" s="95"/>
+      <c r="W19" s="95"/>
+      <c r="X19" s="95"/>
+      <c r="Y19" s="104"/>
+      <c r="Z19" s="104"/>
+      <c r="AA19" s="104"/>
+      <c r="AB19" s="104"/>
+      <c r="AC19" s="104"/>
+      <c r="AD19" s="104"/>
+      <c r="AE19" s="104"/>
+      <c r="AF19" s="104"/>
+      <c r="AG19" s="104"/>
+      <c r="AH19" s="104"/>
+      <c r="AI19" s="104"/>
+      <c r="AJ19" s="104"/>
+      <c r="AK19" s="104"/>
+      <c r="AL19" s="104"/>
+      <c r="AM19" s="104"/>
+      <c r="AN19" s="116"/>
+      <c r="AO19" s="141"/>
+      <c r="AP19" s="104"/>
+      <c r="AQ19" s="104"/>
+      <c r="AR19" s="104"/>
+      <c r="AS19" s="104"/>
+      <c r="AT19" s="104"/>
+      <c r="AU19" s="116"/>
+      <c r="AW19" s="124"/>
+      <c r="AX19" s="126"/>
+      <c r="AZ19" s="154"/>
+      <c r="BA19" s="104"/>
+      <c r="BB19" s="104"/>
+      <c r="BC19" s="104"/>
+      <c r="BD19" s="104"/>
+      <c r="BE19" s="104"/>
+      <c r="BF19" s="104"/>
+      <c r="BG19" s="104"/>
+      <c r="BH19" s="104"/>
+      <c r="BI19" s="104"/>
+      <c r="BJ19" s="104"/>
+      <c r="BK19" s="104"/>
+      <c r="BL19" s="104"/>
+      <c r="BM19" s="104"/>
+      <c r="BN19" s="104"/>
+      <c r="BO19" s="104"/>
+      <c r="BP19" s="104"/>
+      <c r="BQ19" s="104"/>
+      <c r="BR19" s="104"/>
+      <c r="BS19" s="116"/>
       <c r="BT19" s="4"/>
-      <c r="BU19" s="37"/>
+      <c r="BU19" s="35"/>
     </row>
     <row r="20" spans="1:73" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="39"/>
+      <c r="A20" s="37"/>
       <c r="B20" s="12"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="71"/>
-      <c r="K20" s="120"/>
-      <c r="L20" s="117"/>
-      <c r="M20" s="135"/>
-      <c r="N20" s="79"/>
-      <c r="O20" s="79"/>
-      <c r="P20" s="79"/>
-      <c r="Q20" s="79"/>
-      <c r="R20" s="79"/>
-      <c r="S20" s="79"/>
-      <c r="T20" s="79"/>
-      <c r="U20" s="79"/>
-      <c r="V20" s="79"/>
-      <c r="W20" s="79"/>
-      <c r="X20" s="79"/>
-      <c r="Y20" s="63"/>
-      <c r="Z20" s="63"/>
-      <c r="AA20" s="63"/>
-      <c r="AB20" s="63"/>
-      <c r="AC20" s="63"/>
-      <c r="AD20" s="63"/>
-      <c r="AE20" s="63"/>
-      <c r="AF20" s="63"/>
-      <c r="AG20" s="63"/>
-      <c r="AH20" s="63"/>
-      <c r="AI20" s="63"/>
-      <c r="AJ20" s="63"/>
-      <c r="AK20" s="63"/>
-      <c r="AL20" s="63"/>
-      <c r="AM20" s="63"/>
-      <c r="AN20" s="77"/>
-      <c r="AO20" s="139"/>
-      <c r="AP20" s="63"/>
-      <c r="AQ20" s="63"/>
-      <c r="AR20" s="63"/>
-      <c r="AS20" s="63"/>
-      <c r="AT20" s="63"/>
-      <c r="AU20" s="77"/>
-      <c r="AW20" s="70"/>
-      <c r="AX20" s="71"/>
-      <c r="AZ20" s="60"/>
-      <c r="BA20" s="63"/>
-      <c r="BB20" s="63"/>
-      <c r="BC20" s="63"/>
-      <c r="BD20" s="63"/>
-      <c r="BE20" s="63"/>
-      <c r="BF20" s="63"/>
-      <c r="BG20" s="63"/>
-      <c r="BH20" s="63"/>
-      <c r="BI20" s="63"/>
-      <c r="BJ20" s="63"/>
-      <c r="BK20" s="63"/>
-      <c r="BL20" s="63"/>
-      <c r="BM20" s="63"/>
-      <c r="BN20" s="63"/>
-      <c r="BO20" s="63"/>
-      <c r="BP20" s="63"/>
-      <c r="BQ20" s="63"/>
-      <c r="BR20" s="63"/>
-      <c r="BS20" s="77"/>
+      <c r="H20" s="124"/>
+      <c r="I20" s="126"/>
+      <c r="K20" s="160"/>
+      <c r="L20" s="157"/>
+      <c r="M20" s="137"/>
+      <c r="N20" s="95"/>
+      <c r="O20" s="95"/>
+      <c r="P20" s="95"/>
+      <c r="Q20" s="95"/>
+      <c r="R20" s="95"/>
+      <c r="S20" s="95"/>
+      <c r="T20" s="95"/>
+      <c r="U20" s="95"/>
+      <c r="V20" s="95"/>
+      <c r="W20" s="95"/>
+      <c r="X20" s="95"/>
+      <c r="Y20" s="104"/>
+      <c r="Z20" s="104"/>
+      <c r="AA20" s="104"/>
+      <c r="AB20" s="104"/>
+      <c r="AC20" s="104"/>
+      <c r="AD20" s="104"/>
+      <c r="AE20" s="104"/>
+      <c r="AF20" s="104"/>
+      <c r="AG20" s="104"/>
+      <c r="AH20" s="104"/>
+      <c r="AI20" s="104"/>
+      <c r="AJ20" s="104"/>
+      <c r="AK20" s="104"/>
+      <c r="AL20" s="104"/>
+      <c r="AM20" s="104"/>
+      <c r="AN20" s="116"/>
+      <c r="AO20" s="141"/>
+      <c r="AP20" s="104"/>
+      <c r="AQ20" s="104"/>
+      <c r="AR20" s="104"/>
+      <c r="AS20" s="104"/>
+      <c r="AT20" s="104"/>
+      <c r="AU20" s="116"/>
+      <c r="AW20" s="124"/>
+      <c r="AX20" s="126"/>
+      <c r="AZ20" s="154"/>
+      <c r="BA20" s="104"/>
+      <c r="BB20" s="104"/>
+      <c r="BC20" s="104"/>
+      <c r="BD20" s="104"/>
+      <c r="BE20" s="104"/>
+      <c r="BF20" s="104"/>
+      <c r="BG20" s="104"/>
+      <c r="BH20" s="104"/>
+      <c r="BI20" s="104"/>
+      <c r="BJ20" s="104"/>
+      <c r="BK20" s="104"/>
+      <c r="BL20" s="104"/>
+      <c r="BM20" s="104"/>
+      <c r="BN20" s="104"/>
+      <c r="BO20" s="104"/>
+      <c r="BP20" s="104"/>
+      <c r="BQ20" s="104"/>
+      <c r="BR20" s="104"/>
+      <c r="BS20" s="116"/>
       <c r="BT20" s="4"/>
-      <c r="BU20" s="37"/>
+      <c r="BU20" s="35"/>
     </row>
     <row r="21" spans="1:73" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="39"/>
+      <c r="A21" s="37"/>
       <c r="B21" s="12"/>
-      <c r="H21" s="70"/>
-      <c r="I21" s="71"/>
-      <c r="K21" s="120"/>
-      <c r="L21" s="117"/>
-      <c r="M21" s="135"/>
-      <c r="N21" s="79"/>
-      <c r="O21" s="79"/>
-      <c r="P21" s="79"/>
-      <c r="Q21" s="79"/>
-      <c r="R21" s="79"/>
-      <c r="S21" s="79"/>
-      <c r="T21" s="79"/>
-      <c r="U21" s="79"/>
-      <c r="V21" s="79"/>
-      <c r="W21" s="79"/>
-      <c r="X21" s="79"/>
-      <c r="Y21" s="63"/>
-      <c r="Z21" s="63"/>
-      <c r="AA21" s="63"/>
-      <c r="AB21" s="63"/>
-      <c r="AC21" s="63"/>
-      <c r="AD21" s="63"/>
-      <c r="AE21" s="63"/>
-      <c r="AF21" s="63"/>
-      <c r="AG21" s="63"/>
-      <c r="AH21" s="63"/>
-      <c r="AI21" s="63"/>
-      <c r="AJ21" s="63"/>
-      <c r="AK21" s="63"/>
-      <c r="AL21" s="63"/>
-      <c r="AM21" s="63"/>
-      <c r="AN21" s="77"/>
-      <c r="AO21" s="139"/>
-      <c r="AP21" s="63"/>
-      <c r="AQ21" s="63"/>
-      <c r="AR21" s="63"/>
-      <c r="AS21" s="63"/>
-      <c r="AT21" s="63"/>
-      <c r="AU21" s="77"/>
-      <c r="AW21" s="70"/>
-      <c r="AX21" s="71"/>
-      <c r="AZ21" s="60"/>
-      <c r="BA21" s="63"/>
-      <c r="BB21" s="63"/>
-      <c r="BC21" s="63"/>
-      <c r="BD21" s="63"/>
-      <c r="BE21" s="63"/>
-      <c r="BF21" s="63"/>
-      <c r="BG21" s="63"/>
-      <c r="BH21" s="63"/>
-      <c r="BI21" s="63"/>
-      <c r="BJ21" s="63"/>
-      <c r="BK21" s="63"/>
-      <c r="BL21" s="63"/>
-      <c r="BM21" s="63"/>
-      <c r="BN21" s="63"/>
-      <c r="BO21" s="63"/>
-      <c r="BP21" s="63"/>
-      <c r="BQ21" s="63"/>
-      <c r="BR21" s="63"/>
-      <c r="BS21" s="77"/>
+      <c r="H21" s="124"/>
+      <c r="I21" s="126"/>
+      <c r="K21" s="160"/>
+      <c r="L21" s="157"/>
+      <c r="M21" s="137"/>
+      <c r="N21" s="95"/>
+      <c r="O21" s="95"/>
+      <c r="P21" s="95"/>
+      <c r="Q21" s="95"/>
+      <c r="R21" s="95"/>
+      <c r="S21" s="95"/>
+      <c r="T21" s="95"/>
+      <c r="U21" s="95"/>
+      <c r="V21" s="95"/>
+      <c r="W21" s="95"/>
+      <c r="X21" s="95"/>
+      <c r="Y21" s="104"/>
+      <c r="Z21" s="104"/>
+      <c r="AA21" s="104"/>
+      <c r="AB21" s="104"/>
+      <c r="AC21" s="104"/>
+      <c r="AD21" s="104"/>
+      <c r="AE21" s="104"/>
+      <c r="AF21" s="104"/>
+      <c r="AG21" s="104"/>
+      <c r="AH21" s="104"/>
+      <c r="AI21" s="104"/>
+      <c r="AJ21" s="104"/>
+      <c r="AK21" s="104"/>
+      <c r="AL21" s="104"/>
+      <c r="AM21" s="104"/>
+      <c r="AN21" s="116"/>
+      <c r="AO21" s="141"/>
+      <c r="AP21" s="104"/>
+      <c r="AQ21" s="104"/>
+      <c r="AR21" s="104"/>
+      <c r="AS21" s="104"/>
+      <c r="AT21" s="104"/>
+      <c r="AU21" s="116"/>
+      <c r="AW21" s="124"/>
+      <c r="AX21" s="126"/>
+      <c r="AZ21" s="154"/>
+      <c r="BA21" s="104"/>
+      <c r="BB21" s="104"/>
+      <c r="BC21" s="104"/>
+      <c r="BD21" s="104"/>
+      <c r="BE21" s="104"/>
+      <c r="BF21" s="104"/>
+      <c r="BG21" s="104"/>
+      <c r="BH21" s="104"/>
+      <c r="BI21" s="104"/>
+      <c r="BJ21" s="104"/>
+      <c r="BK21" s="104"/>
+      <c r="BL21" s="104"/>
+      <c r="BM21" s="104"/>
+      <c r="BN21" s="104"/>
+      <c r="BO21" s="104"/>
+      <c r="BP21" s="104"/>
+      <c r="BQ21" s="104"/>
+      <c r="BR21" s="104"/>
+      <c r="BS21" s="116"/>
       <c r="BT21" s="4"/>
-      <c r="BU21" s="37"/>
+      <c r="BU21" s="35"/>
     </row>
     <row r="22" spans="1:73" ht="22.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="39"/>
+      <c r="A22" s="37"/>
       <c r="B22" s="12"/>
-      <c r="H22" s="70"/>
-      <c r="I22" s="71"/>
-      <c r="K22" s="120"/>
-      <c r="L22" s="117"/>
-      <c r="M22" s="135"/>
-      <c r="N22" s="79"/>
-      <c r="O22" s="79"/>
-      <c r="P22" s="79"/>
-      <c r="Q22" s="79"/>
-      <c r="R22" s="79"/>
-      <c r="S22" s="79"/>
-      <c r="T22" s="79"/>
-      <c r="U22" s="79"/>
-      <c r="V22" s="79"/>
-      <c r="W22" s="79"/>
-      <c r="X22" s="79"/>
-      <c r="Y22" s="63"/>
-      <c r="Z22" s="63"/>
-      <c r="AA22" s="63"/>
-      <c r="AB22" s="63"/>
-      <c r="AC22" s="63"/>
-      <c r="AD22" s="63"/>
-      <c r="AE22" s="63"/>
-      <c r="AF22" s="63"/>
-      <c r="AG22" s="63"/>
-      <c r="AH22" s="63"/>
-      <c r="AI22" s="63"/>
-      <c r="AJ22" s="63"/>
-      <c r="AK22" s="63"/>
-      <c r="AL22" s="63"/>
-      <c r="AM22" s="63"/>
-      <c r="AN22" s="77"/>
-      <c r="AO22" s="140"/>
-      <c r="AP22" s="69"/>
-      <c r="AQ22" s="69"/>
-      <c r="AR22" s="69"/>
-      <c r="AS22" s="69"/>
-      <c r="AT22" s="69"/>
-      <c r="AU22" s="137"/>
-      <c r="AW22" s="70"/>
-      <c r="AX22" s="71"/>
-      <c r="AZ22" s="61"/>
-      <c r="BA22" s="67"/>
-      <c r="BB22" s="67"/>
-      <c r="BC22" s="67"/>
-      <c r="BD22" s="67"/>
-      <c r="BE22" s="67"/>
-      <c r="BF22" s="67"/>
-      <c r="BG22" s="67"/>
-      <c r="BH22" s="67"/>
-      <c r="BI22" s="67"/>
-      <c r="BJ22" s="67"/>
-      <c r="BK22" s="67"/>
-      <c r="BL22" s="67"/>
-      <c r="BM22" s="67"/>
-      <c r="BN22" s="67"/>
-      <c r="BO22" s="67"/>
-      <c r="BP22" s="67"/>
-      <c r="BQ22" s="67"/>
-      <c r="BR22" s="67"/>
-      <c r="BS22" s="105"/>
+      <c r="H22" s="124"/>
+      <c r="I22" s="126"/>
+      <c r="K22" s="160"/>
+      <c r="L22" s="157"/>
+      <c r="M22" s="137"/>
+      <c r="N22" s="95"/>
+      <c r="O22" s="95"/>
+      <c r="P22" s="95"/>
+      <c r="Q22" s="95"/>
+      <c r="R22" s="95"/>
+      <c r="S22" s="95"/>
+      <c r="T22" s="95"/>
+      <c r="U22" s="95"/>
+      <c r="V22" s="95"/>
+      <c r="W22" s="95"/>
+      <c r="X22" s="95"/>
+      <c r="Y22" s="104"/>
+      <c r="Z22" s="104"/>
+      <c r="AA22" s="104"/>
+      <c r="AB22" s="104"/>
+      <c r="AC22" s="104"/>
+      <c r="AD22" s="104"/>
+      <c r="AE22" s="104"/>
+      <c r="AF22" s="104"/>
+      <c r="AG22" s="104"/>
+      <c r="AH22" s="104"/>
+      <c r="AI22" s="104"/>
+      <c r="AJ22" s="104"/>
+      <c r="AK22" s="104"/>
+      <c r="AL22" s="104"/>
+      <c r="AM22" s="104"/>
+      <c r="AN22" s="116"/>
+      <c r="AO22" s="142"/>
+      <c r="AP22" s="94"/>
+      <c r="AQ22" s="94"/>
+      <c r="AR22" s="94"/>
+      <c r="AS22" s="94"/>
+      <c r="AT22" s="94"/>
+      <c r="AU22" s="139"/>
+      <c r="AW22" s="124"/>
+      <c r="AX22" s="126"/>
+      <c r="AZ22" s="155"/>
+      <c r="BA22" s="105"/>
+      <c r="BB22" s="105"/>
+      <c r="BC22" s="105"/>
+      <c r="BD22" s="105"/>
+      <c r="BE22" s="105"/>
+      <c r="BF22" s="105"/>
+      <c r="BG22" s="105"/>
+      <c r="BH22" s="105"/>
+      <c r="BI22" s="105"/>
+      <c r="BJ22" s="105"/>
+      <c r="BK22" s="105"/>
+      <c r="BL22" s="105"/>
+      <c r="BM22" s="105"/>
+      <c r="BN22" s="105"/>
+      <c r="BO22" s="105"/>
+      <c r="BP22" s="105"/>
+      <c r="BQ22" s="105"/>
+      <c r="BR22" s="105"/>
+      <c r="BS22" s="117"/>
       <c r="BT22" s="4"/>
-      <c r="BU22" s="37"/>
+      <c r="BU22" s="35"/>
     </row>
     <row r="23" spans="1:73" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="39"/>
+      <c r="A23" s="37"/>
       <c r="B23" s="12"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="71"/>
-      <c r="K23" s="120"/>
-      <c r="L23" s="117"/>
-      <c r="M23" s="135"/>
-      <c r="N23" s="79"/>
-      <c r="O23" s="79"/>
-      <c r="P23" s="79"/>
-      <c r="Q23" s="79"/>
-      <c r="R23" s="79"/>
-      <c r="S23" s="79"/>
-      <c r="T23" s="79"/>
-      <c r="U23" s="79"/>
-      <c r="V23" s="79"/>
-      <c r="W23" s="79"/>
-      <c r="X23" s="79"/>
-      <c r="Y23" s="63"/>
-      <c r="Z23" s="63"/>
-      <c r="AA23" s="63"/>
-      <c r="AB23" s="63"/>
-      <c r="AC23" s="63"/>
-      <c r="AD23" s="63"/>
-      <c r="AE23" s="63"/>
-      <c r="AF23" s="63"/>
-      <c r="AG23" s="63"/>
-      <c r="AH23" s="63"/>
-      <c r="AI23" s="63"/>
-      <c r="AJ23" s="63"/>
-      <c r="AK23" s="63"/>
-      <c r="AL23" s="63"/>
-      <c r="AM23" s="63"/>
-      <c r="AN23" s="77"/>
-      <c r="AO23" s="29">
+      <c r="H23" s="124"/>
+      <c r="I23" s="126"/>
+      <c r="K23" s="160"/>
+      <c r="L23" s="157"/>
+      <c r="M23" s="137"/>
+      <c r="N23" s="95"/>
+      <c r="O23" s="95"/>
+      <c r="P23" s="95"/>
+      <c r="Q23" s="95"/>
+      <c r="R23" s="95"/>
+      <c r="S23" s="95"/>
+      <c r="T23" s="95"/>
+      <c r="U23" s="95"/>
+      <c r="V23" s="95"/>
+      <c r="W23" s="95"/>
+      <c r="X23" s="95"/>
+      <c r="Y23" s="104"/>
+      <c r="Z23" s="104"/>
+      <c r="AA23" s="104"/>
+      <c r="AB23" s="104"/>
+      <c r="AC23" s="104"/>
+      <c r="AD23" s="104"/>
+      <c r="AE23" s="104"/>
+      <c r="AF23" s="104"/>
+      <c r="AG23" s="104"/>
+      <c r="AH23" s="104"/>
+      <c r="AI23" s="104"/>
+      <c r="AJ23" s="104"/>
+      <c r="AK23" s="104"/>
+      <c r="AL23" s="104"/>
+      <c r="AM23" s="104"/>
+      <c r="AN23" s="116"/>
+      <c r="AO23" s="28">
         <v>17</v>
       </c>
-      <c r="AP23" s="22">
+      <c r="AP23" s="21">
         <v>18</v>
       </c>
-      <c r="AQ23" s="22">
+      <c r="AQ23" s="21">
         <v>19</v>
       </c>
-      <c r="AR23" s="22">
+      <c r="AR23" s="21">
         <v>20</v>
       </c>
-      <c r="AS23" s="22">
+      <c r="AS23" s="21">
         <v>21</v>
       </c>
-      <c r="AT23" s="22">
+      <c r="AT23" s="21">
         <v>22</v>
       </c>
-      <c r="AU23" s="23">
+      <c r="AU23" s="22">
         <v>23</v>
       </c>
-      <c r="AW23" s="70"/>
-      <c r="AX23" s="71"/>
-      <c r="AZ23" s="47">
+      <c r="AW23" s="124"/>
+      <c r="AX23" s="126"/>
+      <c r="AZ23" s="45">
         <v>1</v>
       </c>
-      <c r="BA23" s="42">
+      <c r="BA23" s="40">
         <v>2</v>
       </c>
-      <c r="BB23" s="42">
+      <c r="BB23" s="40">
         <v>3</v>
       </c>
-      <c r="BC23" s="42">
+      <c r="BC23" s="40">
         <v>4</v>
       </c>
-      <c r="BD23" s="42">
+      <c r="BD23" s="40">
         <v>5</v>
       </c>
-      <c r="BE23" s="42">
+      <c r="BE23" s="40">
         <v>6</v>
       </c>
-      <c r="BF23" s="42">
+      <c r="BF23" s="40">
         <v>7</v>
       </c>
-      <c r="BG23" s="42">
+      <c r="BG23" s="40">
         <v>8</v>
       </c>
-      <c r="BH23" s="42">
+      <c r="BH23" s="40">
         <v>9</v>
       </c>
-      <c r="BI23" s="42">
+      <c r="BI23" s="40">
         <v>10</v>
       </c>
-      <c r="BJ23" s="42">
+      <c r="BJ23" s="40">
         <v>11</v>
       </c>
-      <c r="BK23" s="42">
+      <c r="BK23" s="40">
         <v>12</v>
       </c>
-      <c r="BL23" s="42">
+      <c r="BL23" s="40">
         <v>13</v>
       </c>
-      <c r="BM23" s="42">
+      <c r="BM23" s="40">
         <v>14</v>
       </c>
-      <c r="BN23" s="42">
+      <c r="BN23" s="40">
         <v>15</v>
       </c>
-      <c r="BO23" s="42">
+      <c r="BO23" s="40">
         <v>16</v>
       </c>
-      <c r="BP23" s="42">
+      <c r="BP23" s="40">
         <v>17</v>
       </c>
-      <c r="BQ23" s="42">
+      <c r="BQ23" s="40">
         <v>18</v>
       </c>
-      <c r="BR23" s="42">
+      <c r="BR23" s="40">
         <v>19</v>
       </c>
-      <c r="BS23" s="43">
+      <c r="BS23" s="41">
         <v>20</v>
       </c>
       <c r="BT23" s="4"/>
-      <c r="BU23" s="37"/>
+      <c r="BU23" s="35"/>
     </row>
     <row r="24" spans="1:73" ht="22.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="39"/>
+      <c r="A24" s="37"/>
       <c r="B24" s="12"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="71"/>
-      <c r="K24" s="120"/>
-      <c r="L24" s="117"/>
-      <c r="M24" s="135"/>
-      <c r="N24" s="79"/>
-      <c r="O24" s="79"/>
-      <c r="P24" s="79"/>
-      <c r="Q24" s="79"/>
-      <c r="R24" s="79"/>
-      <c r="S24" s="79"/>
-      <c r="T24" s="79"/>
-      <c r="U24" s="79"/>
-      <c r="V24" s="79"/>
-      <c r="W24" s="79"/>
-      <c r="X24" s="79"/>
-      <c r="Y24" s="63"/>
-      <c r="Z24" s="63"/>
-      <c r="AA24" s="63"/>
-      <c r="AB24" s="63"/>
-      <c r="AC24" s="63"/>
-      <c r="AD24" s="63"/>
-      <c r="AE24" s="63"/>
-      <c r="AF24" s="63"/>
-      <c r="AG24" s="63"/>
-      <c r="AH24" s="63"/>
-      <c r="AI24" s="63"/>
-      <c r="AJ24" s="63"/>
-      <c r="AK24" s="63"/>
-      <c r="AL24" s="63"/>
-      <c r="AM24" s="63"/>
-      <c r="AN24" s="77"/>
-      <c r="AO24" s="53"/>
-      <c r="AP24" s="53"/>
-      <c r="AQ24" s="53"/>
-      <c r="AR24" s="53"/>
-      <c r="AS24" s="53"/>
-      <c r="AT24" s="53"/>
-      <c r="AU24" s="53"/>
+      <c r="H24" s="124"/>
+      <c r="I24" s="126"/>
+      <c r="K24" s="160"/>
+      <c r="L24" s="157"/>
+      <c r="M24" s="137"/>
+      <c r="N24" s="95"/>
+      <c r="O24" s="95"/>
+      <c r="P24" s="95"/>
+      <c r="Q24" s="95"/>
+      <c r="R24" s="95"/>
+      <c r="S24" s="95"/>
+      <c r="T24" s="95"/>
+      <c r="U24" s="95"/>
+      <c r="V24" s="95"/>
+      <c r="W24" s="95"/>
+      <c r="X24" s="95"/>
+      <c r="Y24" s="104"/>
+      <c r="Z24" s="104"/>
+      <c r="AA24" s="104"/>
+      <c r="AB24" s="104"/>
+      <c r="AC24" s="104"/>
+      <c r="AD24" s="104"/>
+      <c r="AE24" s="104"/>
+      <c r="AF24" s="104"/>
+      <c r="AG24" s="104"/>
+      <c r="AH24" s="104"/>
+      <c r="AI24" s="104"/>
+      <c r="AJ24" s="104"/>
+      <c r="AK24" s="104"/>
+      <c r="AL24" s="104"/>
+      <c r="AM24" s="104"/>
+      <c r="AN24" s="116"/>
+      <c r="AO24" s="51"/>
+      <c r="AP24" s="51"/>
+      <c r="AQ24" s="51"/>
+      <c r="AR24" s="51"/>
+      <c r="AS24" s="51"/>
+      <c r="AT24" s="51"/>
+      <c r="AU24" s="51"/>
       <c r="AW24" s="6"/>
       <c r="AX24" s="5"/>
-      <c r="AZ24" s="83" t="s">
+      <c r="AZ24" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="BA24" s="83"/>
-      <c r="BB24" s="83"/>
-      <c r="BC24" s="83"/>
-      <c r="BD24" s="83"/>
-      <c r="BE24" s="83"/>
-      <c r="BF24" s="83"/>
-      <c r="BG24" s="83"/>
-      <c r="BH24" s="83"/>
-      <c r="BI24" s="83"/>
-      <c r="BJ24" s="83"/>
-      <c r="BK24" s="83"/>
-      <c r="BL24" s="83"/>
-      <c r="BM24" s="83"/>
-      <c r="BN24" s="83"/>
-      <c r="BO24" s="83"/>
-      <c r="BP24" s="83"/>
-      <c r="BQ24" s="83"/>
-      <c r="BR24" s="83"/>
-      <c r="BS24" s="83"/>
+      <c r="BA24" s="111"/>
+      <c r="BB24" s="111"/>
+      <c r="BC24" s="111"/>
+      <c r="BD24" s="111"/>
+      <c r="BE24" s="111"/>
+      <c r="BF24" s="111"/>
+      <c r="BG24" s="111"/>
+      <c r="BH24" s="111"/>
+      <c r="BI24" s="111"/>
+      <c r="BJ24" s="111"/>
+      <c r="BK24" s="111"/>
+      <c r="BL24" s="111"/>
+      <c r="BM24" s="111"/>
+      <c r="BN24" s="111"/>
+      <c r="BO24" s="111"/>
+      <c r="BP24" s="111"/>
+      <c r="BQ24" s="111"/>
+      <c r="BR24" s="111"/>
+      <c r="BS24" s="111"/>
       <c r="BT24" s="4"/>
-      <c r="BU24" s="37"/>
+      <c r="BU24" s="35"/>
     </row>
     <row r="25" spans="1:73" ht="22.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="39"/>
+      <c r="A25" s="37"/>
       <c r="B25" s="12"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="71"/>
-      <c r="K25" s="121"/>
-      <c r="L25" s="118"/>
-      <c r="M25" s="136"/>
-      <c r="N25" s="115"/>
-      <c r="O25" s="115"/>
-      <c r="P25" s="115"/>
-      <c r="Q25" s="115"/>
-      <c r="R25" s="115"/>
-      <c r="S25" s="115"/>
-      <c r="T25" s="115"/>
-      <c r="U25" s="115"/>
-      <c r="V25" s="115"/>
-      <c r="W25" s="115"/>
-      <c r="X25" s="115"/>
-      <c r="Y25" s="63"/>
-      <c r="Z25" s="63"/>
-      <c r="AA25" s="63"/>
-      <c r="AB25" s="63"/>
-      <c r="AC25" s="63"/>
-      <c r="AD25" s="63"/>
-      <c r="AE25" s="63"/>
-      <c r="AF25" s="63"/>
-      <c r="AG25" s="63"/>
-      <c r="AH25" s="63"/>
-      <c r="AI25" s="63"/>
-      <c r="AJ25" s="63"/>
-      <c r="AK25" s="63"/>
-      <c r="AL25" s="63"/>
-      <c r="AM25" s="63"/>
-      <c r="AN25" s="77"/>
-      <c r="AO25" s="53"/>
-      <c r="AP25" s="53"/>
-      <c r="AQ25" s="53"/>
-      <c r="AR25" s="53"/>
-      <c r="AS25" s="53"/>
-      <c r="AT25" s="53"/>
-      <c r="AU25" s="53"/>
+      <c r="H25" s="124"/>
+      <c r="I25" s="126"/>
+      <c r="K25" s="161"/>
+      <c r="L25" s="158"/>
+      <c r="M25" s="138"/>
+      <c r="N25" s="135"/>
+      <c r="O25" s="135"/>
+      <c r="P25" s="135"/>
+      <c r="Q25" s="135"/>
+      <c r="R25" s="135"/>
+      <c r="S25" s="135"/>
+      <c r="T25" s="135"/>
+      <c r="U25" s="135"/>
+      <c r="V25" s="135"/>
+      <c r="W25" s="135"/>
+      <c r="X25" s="135"/>
+      <c r="Y25" s="104"/>
+      <c r="Z25" s="104"/>
+      <c r="AA25" s="104"/>
+      <c r="AB25" s="104"/>
+      <c r="AC25" s="104"/>
+      <c r="AD25" s="104"/>
+      <c r="AE25" s="104"/>
+      <c r="AF25" s="104"/>
+      <c r="AG25" s="104"/>
+      <c r="AH25" s="104"/>
+      <c r="AI25" s="104"/>
+      <c r="AJ25" s="104"/>
+      <c r="AK25" s="104"/>
+      <c r="AL25" s="104"/>
+      <c r="AM25" s="104"/>
+      <c r="AN25" s="116"/>
+      <c r="AO25" s="51"/>
+      <c r="AP25" s="51"/>
+      <c r="AQ25" s="51"/>
+      <c r="AR25" s="51"/>
+      <c r="AS25" s="51"/>
+      <c r="AT25" s="51"/>
+      <c r="AU25" s="51"/>
       <c r="AW25" s="6"/>
       <c r="AX25" s="5"/>
       <c r="BT25" s="4"/>
-      <c r="BU25" s="37"/>
+      <c r="BU25" s="35"/>
     </row>
     <row r="26" spans="1:73" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="39"/>
+      <c r="A26" s="37"/>
       <c r="B26" s="12"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="71"/>
-      <c r="K26" s="40" t="s">
+      <c r="H26" s="124"/>
+      <c r="I26" s="126"/>
+      <c r="K26" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="L26" s="41" t="s">
+      <c r="L26" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="M26" s="41" t="s">
+      <c r="M26" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="N26" s="41" t="s">
+      <c r="N26" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="O26" s="41" t="s">
+      <c r="O26" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="P26" s="41" t="s">
+      <c r="P26" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="Q26" s="41" t="s">
+      <c r="Q26" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="R26" s="41" t="s">
+      <c r="R26" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="S26" s="41" t="s">
+      <c r="S26" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="T26" s="41" t="s">
+      <c r="T26" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="U26" s="41" t="s">
+      <c r="U26" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="V26" s="41" t="s">
+      <c r="V26" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="W26" s="41" t="s">
-        <v>86</v>
-      </c>
-      <c r="X26" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y26" s="42">
+      <c r="W26" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="X26" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y26" s="40">
         <v>1</v>
       </c>
-      <c r="Z26" s="42">
+      <c r="Z26" s="40">
         <v>2</v>
       </c>
-      <c r="AA26" s="42">
+      <c r="AA26" s="40">
         <v>3</v>
       </c>
-      <c r="AB26" s="42">
+      <c r="AB26" s="40">
         <v>4</v>
       </c>
-      <c r="AC26" s="42">
+      <c r="AC26" s="40">
         <v>5</v>
       </c>
-      <c r="AD26" s="42">
+      <c r="AD26" s="40">
         <v>6</v>
       </c>
-      <c r="AE26" s="42">
+      <c r="AE26" s="40">
         <v>7</v>
       </c>
-      <c r="AF26" s="42">
+      <c r="AF26" s="40">
         <v>8</v>
       </c>
-      <c r="AG26" s="42">
+      <c r="AG26" s="40">
         <v>9</v>
       </c>
-      <c r="AH26" s="42">
+      <c r="AH26" s="40">
         <v>10</v>
       </c>
-      <c r="AI26" s="42">
+      <c r="AI26" s="40">
         <v>11</v>
       </c>
-      <c r="AJ26" s="42">
+      <c r="AJ26" s="40">
         <v>12</v>
       </c>
-      <c r="AK26" s="42">
+      <c r="AK26" s="40">
         <v>13</v>
       </c>
-      <c r="AL26" s="42">
+      <c r="AL26" s="40">
         <v>14</v>
       </c>
-      <c r="AM26" s="42">
+      <c r="AM26" s="40">
         <v>15</v>
       </c>
-      <c r="AN26" s="43">
+      <c r="AN26" s="41">
         <v>16</v>
       </c>
-      <c r="AO26" s="53"/>
-      <c r="AP26" s="53"/>
-      <c r="AQ26" s="53"/>
-      <c r="AR26" s="53"/>
-      <c r="AS26" s="53"/>
-      <c r="AT26" s="53"/>
-      <c r="AU26" s="53"/>
+      <c r="AO26" s="51"/>
+      <c r="AP26" s="51"/>
+      <c r="AQ26" s="51"/>
+      <c r="AR26" s="51"/>
+      <c r="AS26" s="51"/>
+      <c r="AT26" s="51"/>
+      <c r="AU26" s="51"/>
       <c r="AW26" s="6"/>
       <c r="AX26" s="5"/>
       <c r="BT26" s="4"/>
-      <c r="BU26" s="37"/>
+      <c r="BU26" s="35"/>
     </row>
     <row r="27" spans="1:73" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="39"/>
+      <c r="A27" s="37"/>
       <c r="B27" s="12"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="71"/>
-      <c r="X27" s="16"/>
-      <c r="Y27" s="141" t="s">
+      <c r="H27" s="124"/>
+      <c r="I27" s="126"/>
+      <c r="X27" s="15"/>
+      <c r="Y27" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="Z27" s="141"/>
-      <c r="AA27" s="141"/>
-      <c r="AB27" s="141"/>
-      <c r="AC27" s="141"/>
-      <c r="AD27" s="141"/>
-      <c r="AE27" s="141"/>
-      <c r="AF27" s="141"/>
-      <c r="AG27" s="141"/>
-      <c r="AH27" s="141"/>
-      <c r="AI27" s="141"/>
-      <c r="AJ27" s="141"/>
-      <c r="AK27" s="141"/>
-      <c r="AL27" s="141"/>
-      <c r="AM27" s="141"/>
-      <c r="AN27" s="141"/>
-      <c r="AO27" s="141"/>
-      <c r="AP27" s="141"/>
-      <c r="AQ27" s="141"/>
-      <c r="AR27" s="141"/>
-      <c r="AS27" s="141"/>
-      <c r="AT27" s="141"/>
-      <c r="AU27" s="141"/>
+      <c r="Z27" s="143"/>
+      <c r="AA27" s="143"/>
+      <c r="AB27" s="143"/>
+      <c r="AC27" s="143"/>
+      <c r="AD27" s="143"/>
+      <c r="AE27" s="143"/>
+      <c r="AF27" s="143"/>
+      <c r="AG27" s="143"/>
+      <c r="AH27" s="143"/>
+      <c r="AI27" s="143"/>
+      <c r="AJ27" s="143"/>
+      <c r="AK27" s="143"/>
+      <c r="AL27" s="143"/>
+      <c r="AM27" s="143"/>
+      <c r="AN27" s="143"/>
+      <c r="AO27" s="143"/>
+      <c r="AP27" s="143"/>
+      <c r="AQ27" s="143"/>
+      <c r="AR27" s="143"/>
+      <c r="AS27" s="143"/>
+      <c r="AT27" s="143"/>
+      <c r="AU27" s="143"/>
       <c r="AW27" s="6"/>
       <c r="AX27" s="5"/>
-      <c r="AZ27" s="125"/>
-      <c r="BB27" s="125"/>
-      <c r="BF27" s="125"/>
-      <c r="BH27" s="125"/>
-      <c r="BL27" s="125"/>
-      <c r="BN27" s="125"/>
-      <c r="BQ27" s="125"/>
-      <c r="BS27" s="125"/>
+      <c r="AZ27" s="91"/>
+      <c r="BB27" s="91"/>
+      <c r="BF27" s="91"/>
+      <c r="BH27" s="91"/>
+      <c r="BL27" s="91"/>
+      <c r="BN27" s="91"/>
+      <c r="BQ27" s="91"/>
+      <c r="BS27" s="91"/>
       <c r="BT27" s="4"/>
-      <c r="BU27" s="37"/>
+      <c r="BU27" s="35"/>
     </row>
     <row r="28" spans="1:73" ht="22.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="39"/>
+      <c r="A28" s="37"/>
       <c r="B28" s="12"/>
-      <c r="H28" s="70"/>
-      <c r="I28" s="71"/>
+      <c r="H28" s="124"/>
+      <c r="I28" s="126"/>
       <c r="AW28" s="6"/>
       <c r="AX28" s="5"/>
-      <c r="AZ28" s="126"/>
-      <c r="BB28" s="126"/>
-      <c r="BF28" s="126"/>
-      <c r="BH28" s="126"/>
-      <c r="BL28" s="126"/>
-      <c r="BN28" s="126"/>
-      <c r="BQ28" s="126"/>
-      <c r="BS28" s="126"/>
+      <c r="AZ28" s="92"/>
+      <c r="BB28" s="92"/>
+      <c r="BF28" s="92"/>
+      <c r="BH28" s="92"/>
+      <c r="BL28" s="92"/>
+      <c r="BN28" s="92"/>
+      <c r="BQ28" s="92"/>
+      <c r="BS28" s="92"/>
       <c r="BT28" s="4"/>
-      <c r="BU28" s="37"/>
+      <c r="BU28" s="35"/>
     </row>
     <row r="29" spans="1:73" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="39"/>
+      <c r="A29" s="37"/>
       <c r="B29" s="12"/>
-      <c r="H29" s="103"/>
-      <c r="I29" s="150"/>
-      <c r="J29" s="148"/>
-      <c r="K29" s="148"/>
-      <c r="L29" s="148"/>
-      <c r="M29" s="148"/>
-      <c r="N29" s="148"/>
-      <c r="O29" s="148"/>
-      <c r="P29" s="148"/>
-      <c r="Q29" s="148"/>
-      <c r="R29" s="148"/>
-      <c r="S29" s="148"/>
-      <c r="T29" s="148"/>
-      <c r="U29" s="148"/>
-      <c r="V29" s="148"/>
+      <c r="H29" s="110"/>
+      <c r="I29" s="109"/>
+      <c r="J29" s="108"/>
+      <c r="K29" s="108"/>
+      <c r="L29" s="108"/>
+      <c r="M29" s="108"/>
+      <c r="N29" s="108"/>
+      <c r="O29" s="108"/>
+      <c r="P29" s="108"/>
+      <c r="Q29" s="108"/>
+      <c r="R29" s="108"/>
+      <c r="S29" s="108"/>
+      <c r="T29" s="108"/>
+      <c r="U29" s="108"/>
+      <c r="V29" s="108"/>
       <c r="W29" s="9"/>
       <c r="X29" s="9"/>
       <c r="Y29" s="9"/>
       <c r="Z29" s="9"/>
       <c r="AA29" s="9"/>
       <c r="AB29" s="9"/>
-      <c r="AC29" s="57" t="s">
+      <c r="AC29" s="215" t="s">
         <v>7</v>
       </c>
-      <c r="AD29" s="57"/>
-      <c r="AE29" s="57"/>
-      <c r="AF29" s="57"/>
-      <c r="AG29" s="57"/>
-      <c r="AH29" s="57"/>
-      <c r="AI29" s="57"/>
-      <c r="AJ29" s="57"/>
-      <c r="AK29" s="57"/>
-      <c r="AL29" s="57"/>
+      <c r="AD29" s="215"/>
+      <c r="AE29" s="215"/>
+      <c r="AF29" s="215"/>
+      <c r="AG29" s="215"/>
+      <c r="AH29" s="215"/>
+      <c r="AI29" s="215"/>
+      <c r="AJ29" s="215"/>
+      <c r="AK29" s="215"/>
+      <c r="AL29" s="215"/>
       <c r="AM29" s="9"/>
       <c r="AN29" s="9"/>
       <c r="AO29" s="9"/>
@@ -4263,203 +4562,607 @@
       <c r="AT29" s="9"/>
       <c r="AU29" s="9"/>
       <c r="AV29" s="9"/>
-      <c r="AW29" s="52"/>
-      <c r="AX29" s="52"/>
+      <c r="AW29" s="50"/>
+      <c r="AX29" s="50"/>
       <c r="AY29" s="9"/>
-      <c r="AZ29" s="126"/>
+      <c r="AZ29" s="92"/>
       <c r="BA29" s="9"/>
-      <c r="BB29" s="126"/>
+      <c r="BB29" s="92"/>
       <c r="BC29" s="9"/>
       <c r="BD29" s="9"/>
       <c r="BE29" s="9"/>
-      <c r="BF29" s="126"/>
+      <c r="BF29" s="92"/>
       <c r="BG29" s="9"/>
-      <c r="BH29" s="126"/>
-      <c r="BI29" s="128" t="s">
+      <c r="BH29" s="92"/>
+      <c r="BI29" s="129" t="s">
         <v>49</v>
       </c>
-      <c r="BJ29" s="129"/>
-      <c r="BK29" s="130"/>
-      <c r="BL29" s="126"/>
-      <c r="BM29" s="30"/>
-      <c r="BN29" s="126"/>
-      <c r="BO29" s="30"/>
+      <c r="BJ29" s="130"/>
+      <c r="BK29" s="131"/>
+      <c r="BL29" s="92"/>
+      <c r="BM29" s="29"/>
+      <c r="BN29" s="92"/>
+      <c r="BO29" s="29"/>
       <c r="BP29" s="9"/>
-      <c r="BQ29" s="126"/>
+      <c r="BQ29" s="92"/>
       <c r="BR29" s="9"/>
-      <c r="BS29" s="126"/>
+      <c r="BS29" s="92"/>
       <c r="BT29" s="10"/>
-      <c r="BU29" s="37"/>
+      <c r="BU29" s="35"/>
     </row>
     <row r="30" spans="1:73" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="39"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="151"/>
-      <c r="I30" s="149"/>
-      <c r="J30" s="149"/>
-      <c r="K30" s="149"/>
-      <c r="L30" s="149"/>
-      <c r="M30" s="149"/>
-      <c r="N30" s="149"/>
-      <c r="O30" s="149"/>
-      <c r="P30" s="149"/>
-      <c r="Q30" s="149"/>
-      <c r="R30" s="149"/>
-      <c r="S30" s="149"/>
-      <c r="T30" s="149"/>
-      <c r="U30" s="149"/>
-      <c r="V30" s="149"/>
-      <c r="W30" s="7"/>
-      <c r="X30" s="7"/>
-      <c r="Y30" s="7"/>
-      <c r="Z30" s="7"/>
-      <c r="AA30" s="7"/>
-      <c r="AB30" s="7"/>
-      <c r="AC30" s="58"/>
-      <c r="AD30" s="58"/>
-      <c r="AE30" s="58"/>
-      <c r="AF30" s="58"/>
-      <c r="AG30" s="58"/>
-      <c r="AH30" s="58"/>
-      <c r="AI30" s="58"/>
-      <c r="AJ30" s="58"/>
-      <c r="AK30" s="58"/>
-      <c r="AL30" s="58"/>
-      <c r="AM30" s="7"/>
-      <c r="AN30" s="7"/>
-      <c r="AO30" s="7"/>
-      <c r="AP30" s="7"/>
-      <c r="AQ30" s="7"/>
-      <c r="AR30" s="7"/>
-      <c r="AS30" s="7"/>
-      <c r="AT30" s="7"/>
-      <c r="AU30" s="7"/>
-      <c r="AV30" s="7"/>
-      <c r="AW30" s="7"/>
-      <c r="AX30" s="7"/>
-      <c r="AY30" s="7"/>
-      <c r="AZ30" s="127"/>
-      <c r="BA30" s="7"/>
-      <c r="BB30" s="127"/>
-      <c r="BC30" s="7"/>
-      <c r="BD30" s="7"/>
-      <c r="BE30" s="7"/>
-      <c r="BF30" s="127"/>
-      <c r="BG30" s="7"/>
-      <c r="BH30" s="127"/>
-      <c r="BI30" s="131" t="s">
+      <c r="A30" s="37"/>
+      <c r="B30" s="12"/>
+      <c r="H30" s="110"/>
+      <c r="I30" s="109"/>
+      <c r="J30" s="109"/>
+      <c r="K30" s="109"/>
+      <c r="L30" s="109"/>
+      <c r="M30" s="109"/>
+      <c r="N30" s="109"/>
+      <c r="O30" s="109"/>
+      <c r="P30" s="109"/>
+      <c r="Q30" s="109"/>
+      <c r="R30" s="109"/>
+      <c r="S30" s="109"/>
+      <c r="T30" s="109"/>
+      <c r="U30" s="109"/>
+      <c r="V30" s="109"/>
+      <c r="W30" s="50"/>
+      <c r="X30" s="50"/>
+      <c r="Y30" s="50"/>
+      <c r="Z30" s="50"/>
+      <c r="AA30" s="50"/>
+      <c r="AB30" s="50"/>
+      <c r="AC30" s="216"/>
+      <c r="AD30" s="216"/>
+      <c r="AE30" s="216"/>
+      <c r="AF30" s="216"/>
+      <c r="AG30" s="216"/>
+      <c r="AH30" s="216"/>
+      <c r="AI30" s="216"/>
+      <c r="AJ30" s="216"/>
+      <c r="AK30" s="216"/>
+      <c r="AL30" s="216"/>
+      <c r="AM30" s="50"/>
+      <c r="AN30" s="50"/>
+      <c r="AO30" s="50"/>
+      <c r="AP30" s="50"/>
+      <c r="AQ30" s="50"/>
+      <c r="AR30" s="50"/>
+      <c r="AS30" s="50"/>
+      <c r="AT30" s="50"/>
+      <c r="AU30" s="50"/>
+      <c r="AV30" s="50"/>
+      <c r="AW30" s="50"/>
+      <c r="AX30" s="50"/>
+      <c r="AY30" s="196"/>
+      <c r="AZ30" s="92"/>
+      <c r="BA30" s="50"/>
+      <c r="BB30" s="92"/>
+      <c r="BC30" s="6"/>
+      <c r="BD30" s="50"/>
+      <c r="BE30" s="50"/>
+      <c r="BF30" s="92"/>
+      <c r="BG30" s="50"/>
+      <c r="BH30" s="92"/>
+      <c r="BI30" s="132" t="s">
         <v>50</v>
       </c>
-      <c r="BJ30" s="132"/>
-      <c r="BK30" s="133"/>
-      <c r="BL30" s="127"/>
-      <c r="BM30" s="31"/>
-      <c r="BN30" s="127"/>
-      <c r="BO30" s="31"/>
-      <c r="BP30" s="7"/>
-      <c r="BQ30" s="127"/>
-      <c r="BR30" s="7"/>
-      <c r="BS30" s="127"/>
-      <c r="BT30" s="8"/>
-      <c r="BU30" s="37"/>
+      <c r="BJ30" s="133"/>
+      <c r="BK30" s="134"/>
+      <c r="BL30" s="92"/>
+      <c r="BM30" s="209"/>
+      <c r="BN30" s="92"/>
+      <c r="BO30" s="58"/>
+      <c r="BP30" s="50"/>
+      <c r="BQ30" s="92"/>
+      <c r="BR30" s="213"/>
+      <c r="BS30" s="92"/>
+      <c r="BT30" s="214"/>
+      <c r="BU30" s="35"/>
     </row>
-    <row r="31" spans="1:73" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="34"/>
-      <c r="B31" s="35"/>
-      <c r="C31" s="35"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="35"/>
-      <c r="J31" s="35"/>
-      <c r="K31" s="35"/>
-      <c r="L31" s="35"/>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
-      <c r="O31" s="35"/>
-      <c r="P31" s="35"/>
-      <c r="Q31" s="35"/>
-      <c r="R31" s="35"/>
-      <c r="S31" s="35"/>
-      <c r="T31" s="35"/>
-      <c r="U31" s="35"/>
-      <c r="V31" s="35"/>
-      <c r="W31" s="35"/>
-      <c r="X31" s="35"/>
-      <c r="Y31" s="35"/>
-      <c r="Z31" s="49"/>
-      <c r="AA31" s="49"/>
-      <c r="AB31" s="49"/>
-      <c r="AC31" s="49"/>
-      <c r="AD31" s="49"/>
-      <c r="AE31" s="49"/>
-      <c r="AF31" s="49"/>
-      <c r="AG31" s="49"/>
-      <c r="AH31" s="49"/>
-      <c r="AI31" s="49"/>
-      <c r="AJ31" s="49"/>
-      <c r="AK31" s="49"/>
-      <c r="AL31" s="49"/>
-      <c r="AM31" s="49"/>
-      <c r="AN31" s="49"/>
-      <c r="AO31" s="49"/>
-      <c r="AP31" s="49"/>
-      <c r="AQ31" s="49"/>
-      <c r="AR31" s="49"/>
-      <c r="AS31" s="49"/>
-      <c r="AT31" s="49"/>
-      <c r="AU31" s="49"/>
-      <c r="AV31" s="49"/>
-      <c r="AW31" s="49"/>
-      <c r="AX31" s="35"/>
-      <c r="AY31" s="35"/>
-      <c r="AZ31" s="35"/>
-      <c r="BA31" s="35"/>
-      <c r="BB31" s="35"/>
-      <c r="BC31" s="35"/>
-      <c r="BD31" s="35"/>
-      <c r="BE31" s="35"/>
-      <c r="BF31" s="35"/>
-      <c r="BG31" s="35"/>
-      <c r="BH31" s="35"/>
-      <c r="BI31" s="35"/>
-      <c r="BJ31" s="35"/>
-      <c r="BK31" s="35"/>
-      <c r="BL31" s="35"/>
-      <c r="BM31" s="35"/>
-      <c r="BN31" s="35"/>
-      <c r="BO31" s="35"/>
-      <c r="BP31" s="35"/>
-      <c r="BQ31" s="35"/>
-      <c r="BR31" s="35"/>
-      <c r="BS31" s="35"/>
-      <c r="BT31" s="35"/>
-      <c r="BU31" s="36"/>
+    <row r="31" spans="1:73" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="37"/>
+      <c r="B31" s="12"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="56"/>
+      <c r="J31" s="59"/>
+      <c r="K31" s="62" t="s">
+        <v>118</v>
+      </c>
+      <c r="L31" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="M31" s="63" t="s">
+        <v>120</v>
+      </c>
+      <c r="N31" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="O31" s="63" t="s">
+        <v>122</v>
+      </c>
+      <c r="P31" s="63" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q31" s="63" t="s">
+        <v>124</v>
+      </c>
+      <c r="R31" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="S31" s="63" t="s">
+        <v>126</v>
+      </c>
+      <c r="T31" s="63" t="s">
+        <v>127</v>
+      </c>
+      <c r="U31" s="63" t="s">
+        <v>128</v>
+      </c>
+      <c r="V31" s="63" t="s">
+        <v>129</v>
+      </c>
+      <c r="W31" s="63" t="s">
+        <v>130</v>
+      </c>
+      <c r="X31" s="63" t="s">
+        <v>131</v>
+      </c>
+      <c r="Y31" s="63" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z31" s="63" t="s">
+        <v>133</v>
+      </c>
+      <c r="AA31" s="63" t="s">
+        <v>134</v>
+      </c>
+      <c r="AB31" s="63" t="s">
+        <v>135</v>
+      </c>
+      <c r="AC31" s="63" t="s">
+        <v>136</v>
+      </c>
+      <c r="AD31" s="63" t="s">
+        <v>137</v>
+      </c>
+      <c r="AE31" s="63" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF31" s="63" t="s">
+        <v>139</v>
+      </c>
+      <c r="AG31" s="63" t="s">
+        <v>140</v>
+      </c>
+      <c r="AH31" s="63" t="s">
+        <v>141</v>
+      </c>
+      <c r="AI31" s="63" t="s">
+        <v>142</v>
+      </c>
+      <c r="AJ31" s="63" t="s">
+        <v>143</v>
+      </c>
+      <c r="AK31" s="63" t="s">
+        <v>144</v>
+      </c>
+      <c r="AL31" s="63" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM31" s="63" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN31" s="64" t="s">
+        <v>147</v>
+      </c>
+      <c r="AO31" s="83" t="s">
+        <v>117</v>
+      </c>
+      <c r="AP31" s="83"/>
+      <c r="AQ31" s="83"/>
+      <c r="AR31" s="83"/>
+      <c r="AS31" s="83"/>
+      <c r="AT31" s="83"/>
+      <c r="AU31" s="83"/>
+      <c r="AV31" s="84"/>
+      <c r="AW31" s="50"/>
+      <c r="AX31" s="196"/>
+      <c r="AY31" s="198"/>
+      <c r="AZ31" s="92"/>
+      <c r="BA31" s="200"/>
+      <c r="BB31" s="92"/>
+      <c r="BC31" s="201"/>
+      <c r="BD31" s="202"/>
+      <c r="BE31" s="203"/>
+      <c r="BF31" s="92"/>
+      <c r="BG31" s="200"/>
+      <c r="BH31" s="92"/>
+      <c r="BI31" s="205"/>
+      <c r="BJ31" s="206"/>
+      <c r="BK31" s="207"/>
+      <c r="BL31" s="92"/>
+      <c r="BM31" s="210"/>
+      <c r="BN31" s="92"/>
+      <c r="BO31" s="211"/>
+      <c r="BP31" s="212"/>
+      <c r="BQ31" s="92"/>
+      <c r="BR31" s="67"/>
+      <c r="BS31" s="92"/>
+      <c r="BT31" s="201"/>
+      <c r="BU31" s="35"/>
     </row>
-    <row r="32" spans="1:73" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:73" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="217"/>
+      <c r="H32" s="54"/>
+      <c r="I32" s="57"/>
+      <c r="J32" s="60"/>
+      <c r="K32" s="100"/>
+      <c r="L32" s="94"/>
+      <c r="M32" s="94"/>
+      <c r="N32" s="94"/>
+      <c r="O32" s="94"/>
+      <c r="P32" s="94"/>
+      <c r="Q32" s="94"/>
+      <c r="R32" s="94"/>
+      <c r="S32" s="94"/>
+      <c r="T32" s="94"/>
+      <c r="U32" s="94"/>
+      <c r="V32" s="94"/>
+      <c r="W32" s="94"/>
+      <c r="X32" s="94"/>
+      <c r="Y32" s="94"/>
+      <c r="Z32" s="94"/>
+      <c r="AA32" s="94"/>
+      <c r="AB32" s="94"/>
+      <c r="AC32" s="94"/>
+      <c r="AD32" s="94"/>
+      <c r="AE32" s="94"/>
+      <c r="AF32" s="94"/>
+      <c r="AG32" s="94"/>
+      <c r="AH32" s="94"/>
+      <c r="AI32" s="94"/>
+      <c r="AJ32" s="94"/>
+      <c r="AK32" s="94"/>
+      <c r="AL32" s="94"/>
+      <c r="AM32" s="94"/>
+      <c r="AN32" s="97"/>
+      <c r="AO32" s="85"/>
+      <c r="AP32" s="86"/>
+      <c r="AQ32" s="86"/>
+      <c r="AR32" s="86"/>
+      <c r="AS32" s="86"/>
+      <c r="AT32" s="86"/>
+      <c r="AU32" s="86"/>
+      <c r="AV32" s="87"/>
+      <c r="AW32" s="50"/>
+      <c r="AX32" s="196"/>
+      <c r="AY32" s="197"/>
+      <c r="AZ32" s="92"/>
+      <c r="BA32" s="67"/>
+      <c r="BB32" s="92"/>
+      <c r="BC32" s="65"/>
+      <c r="BD32" s="204"/>
+      <c r="BE32" s="80"/>
+      <c r="BF32" s="92"/>
+      <c r="BG32" s="67"/>
+      <c r="BH32" s="92"/>
+      <c r="BI32" s="75"/>
+      <c r="BJ32" s="208"/>
+      <c r="BK32" s="76"/>
+      <c r="BL32" s="92"/>
+      <c r="BM32" s="73"/>
+      <c r="BN32" s="92"/>
+      <c r="BO32" s="69"/>
+      <c r="BP32" s="70"/>
+      <c r="BQ32" s="92"/>
+      <c r="BR32" s="67"/>
+      <c r="BS32" s="92"/>
+      <c r="BT32" s="65"/>
+      <c r="BU32" s="35"/>
+    </row>
+    <row r="33" spans="1:73" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="217"/>
+      <c r="H33" s="54"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="60"/>
+      <c r="K33" s="101"/>
+      <c r="L33" s="95"/>
+      <c r="M33" s="95"/>
+      <c r="N33" s="95"/>
+      <c r="O33" s="95"/>
+      <c r="P33" s="95"/>
+      <c r="Q33" s="95"/>
+      <c r="R33" s="95"/>
+      <c r="S33" s="95"/>
+      <c r="T33" s="95"/>
+      <c r="U33" s="95"/>
+      <c r="V33" s="95"/>
+      <c r="W33" s="95"/>
+      <c r="X33" s="95"/>
+      <c r="Y33" s="95"/>
+      <c r="Z33" s="95"/>
+      <c r="AA33" s="95"/>
+      <c r="AB33" s="95"/>
+      <c r="AC33" s="95"/>
+      <c r="AD33" s="95"/>
+      <c r="AE33" s="95"/>
+      <c r="AF33" s="95"/>
+      <c r="AG33" s="95"/>
+      <c r="AH33" s="95"/>
+      <c r="AI33" s="95"/>
+      <c r="AJ33" s="95"/>
+      <c r="AK33" s="95"/>
+      <c r="AL33" s="95"/>
+      <c r="AM33" s="95"/>
+      <c r="AN33" s="98"/>
+      <c r="AO33" s="85"/>
+      <c r="AP33" s="86"/>
+      <c r="AQ33" s="86"/>
+      <c r="AR33" s="86"/>
+      <c r="AS33" s="86"/>
+      <c r="AT33" s="86"/>
+      <c r="AU33" s="86"/>
+      <c r="AV33" s="87"/>
+      <c r="AW33" s="50"/>
+      <c r="AX33" s="196"/>
+      <c r="AY33" s="197"/>
+      <c r="AZ33" s="92"/>
+      <c r="BA33" s="67"/>
+      <c r="BB33" s="92"/>
+      <c r="BC33" s="65"/>
+      <c r="BD33" s="204"/>
+      <c r="BE33" s="80"/>
+      <c r="BF33" s="92"/>
+      <c r="BG33" s="67"/>
+      <c r="BH33" s="92"/>
+      <c r="BI33" s="75"/>
+      <c r="BJ33" s="208"/>
+      <c r="BK33" s="76"/>
+      <c r="BL33" s="92"/>
+      <c r="BM33" s="73"/>
+      <c r="BN33" s="92"/>
+      <c r="BO33" s="69"/>
+      <c r="BP33" s="70"/>
+      <c r="BQ33" s="92"/>
+      <c r="BR33" s="67"/>
+      <c r="BS33" s="92"/>
+      <c r="BT33" s="65"/>
+      <c r="BU33" s="35"/>
+    </row>
+    <row r="34" spans="1:73" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="217"/>
+      <c r="H34" s="54"/>
+      <c r="I34" s="57"/>
+      <c r="J34" s="60"/>
+      <c r="K34" s="101"/>
+      <c r="L34" s="95"/>
+      <c r="M34" s="95"/>
+      <c r="N34" s="95"/>
+      <c r="O34" s="95"/>
+      <c r="P34" s="95"/>
+      <c r="Q34" s="95"/>
+      <c r="R34" s="95"/>
+      <c r="S34" s="95"/>
+      <c r="T34" s="95"/>
+      <c r="U34" s="95"/>
+      <c r="V34" s="95"/>
+      <c r="W34" s="95"/>
+      <c r="X34" s="95"/>
+      <c r="Y34" s="95"/>
+      <c r="Z34" s="95"/>
+      <c r="AA34" s="95"/>
+      <c r="AB34" s="95"/>
+      <c r="AC34" s="95"/>
+      <c r="AD34" s="95"/>
+      <c r="AE34" s="95"/>
+      <c r="AF34" s="95"/>
+      <c r="AG34" s="95"/>
+      <c r="AH34" s="95"/>
+      <c r="AI34" s="95"/>
+      <c r="AJ34" s="95"/>
+      <c r="AK34" s="95"/>
+      <c r="AL34" s="95"/>
+      <c r="AM34" s="95"/>
+      <c r="AN34" s="98"/>
+      <c r="AO34" s="85"/>
+      <c r="AP34" s="86"/>
+      <c r="AQ34" s="86"/>
+      <c r="AR34" s="86"/>
+      <c r="AS34" s="86"/>
+      <c r="AT34" s="86"/>
+      <c r="AU34" s="86"/>
+      <c r="AV34" s="87"/>
+      <c r="AW34" s="50"/>
+      <c r="AX34" s="196"/>
+      <c r="AY34" s="197"/>
+      <c r="AZ34" s="92"/>
+      <c r="BA34" s="67"/>
+      <c r="BB34" s="92"/>
+      <c r="BC34" s="65"/>
+      <c r="BD34" s="204"/>
+      <c r="BE34" s="80"/>
+      <c r="BF34" s="92"/>
+      <c r="BG34" s="67"/>
+      <c r="BH34" s="92"/>
+      <c r="BI34" s="75"/>
+      <c r="BJ34" s="208"/>
+      <c r="BK34" s="76"/>
+      <c r="BL34" s="92"/>
+      <c r="BM34" s="73"/>
+      <c r="BN34" s="92"/>
+      <c r="BO34" s="69"/>
+      <c r="BP34" s="70"/>
+      <c r="BQ34" s="92"/>
+      <c r="BR34" s="67"/>
+      <c r="BS34" s="92"/>
+      <c r="BT34" s="65"/>
+      <c r="BU34" s="35"/>
+    </row>
+    <row r="35" spans="1:73" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="37"/>
+      <c r="B35" s="218"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="55"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="61"/>
+      <c r="K35" s="102"/>
+      <c r="L35" s="96"/>
+      <c r="M35" s="96"/>
+      <c r="N35" s="96"/>
+      <c r="O35" s="96"/>
+      <c r="P35" s="96"/>
+      <c r="Q35" s="96"/>
+      <c r="R35" s="96"/>
+      <c r="S35" s="96"/>
+      <c r="T35" s="96"/>
+      <c r="U35" s="96"/>
+      <c r="V35" s="96"/>
+      <c r="W35" s="96"/>
+      <c r="X35" s="96"/>
+      <c r="Y35" s="96"/>
+      <c r="Z35" s="96"/>
+      <c r="AA35" s="96"/>
+      <c r="AB35" s="96"/>
+      <c r="AC35" s="96"/>
+      <c r="AD35" s="96"/>
+      <c r="AE35" s="96"/>
+      <c r="AF35" s="96"/>
+      <c r="AG35" s="96"/>
+      <c r="AH35" s="96"/>
+      <c r="AI35" s="96"/>
+      <c r="AJ35" s="96"/>
+      <c r="AK35" s="96"/>
+      <c r="AL35" s="96"/>
+      <c r="AM35" s="96"/>
+      <c r="AN35" s="99"/>
+      <c r="AO35" s="88"/>
+      <c r="AP35" s="89"/>
+      <c r="AQ35" s="89"/>
+      <c r="AR35" s="89"/>
+      <c r="AS35" s="89"/>
+      <c r="AT35" s="89"/>
+      <c r="AU35" s="89"/>
+      <c r="AV35" s="90"/>
+      <c r="AW35" s="7"/>
+      <c r="AX35" s="7"/>
+      <c r="AY35" s="199"/>
+      <c r="AZ35" s="93"/>
+      <c r="BA35" s="68"/>
+      <c r="BB35" s="93"/>
+      <c r="BC35" s="66"/>
+      <c r="BD35" s="81"/>
+      <c r="BE35" s="82"/>
+      <c r="BF35" s="93"/>
+      <c r="BG35" s="68"/>
+      <c r="BH35" s="93"/>
+      <c r="BI35" s="77"/>
+      <c r="BJ35" s="78"/>
+      <c r="BK35" s="79"/>
+      <c r="BL35" s="93"/>
+      <c r="BM35" s="74"/>
+      <c r="BN35" s="93"/>
+      <c r="BO35" s="71"/>
+      <c r="BP35" s="72"/>
+      <c r="BQ35" s="93"/>
+      <c r="BR35" s="68"/>
+      <c r="BS35" s="93"/>
+      <c r="BT35" s="66"/>
+      <c r="BU35" s="35"/>
+    </row>
+    <row r="36" spans="1:73" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="32"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="33"/>
+      <c r="M36" s="33"/>
+      <c r="N36" s="33"/>
+      <c r="O36" s="33"/>
+      <c r="P36" s="33"/>
+      <c r="Q36" s="33"/>
+      <c r="R36" s="33"/>
+      <c r="S36" s="33"/>
+      <c r="T36" s="33"/>
+      <c r="U36" s="33"/>
+      <c r="V36" s="33"/>
+      <c r="W36" s="33"/>
+      <c r="X36" s="33"/>
+      <c r="Y36" s="33"/>
+      <c r="Z36" s="33"/>
+      <c r="AA36" s="33"/>
+      <c r="AB36" s="33"/>
+      <c r="AC36" s="33"/>
+      <c r="AD36" s="33"/>
+      <c r="AE36" s="33"/>
+      <c r="AF36" s="33"/>
+      <c r="AG36" s="33"/>
+      <c r="AH36" s="33"/>
+      <c r="AI36" s="33"/>
+      <c r="AJ36" s="33"/>
+      <c r="AK36" s="33"/>
+      <c r="AL36" s="33"/>
+      <c r="AM36" s="33"/>
+      <c r="AN36" s="33"/>
+      <c r="AO36" s="33"/>
+      <c r="AP36" s="33"/>
+      <c r="AQ36" s="33"/>
+      <c r="AR36" s="33"/>
+      <c r="AS36" s="33"/>
+      <c r="AT36" s="33"/>
+      <c r="AU36" s="33"/>
+      <c r="AV36" s="33"/>
+      <c r="AW36" s="47"/>
+      <c r="AX36" s="33"/>
+      <c r="AY36" s="33"/>
+      <c r="AZ36" s="33"/>
+      <c r="BA36" s="33"/>
+      <c r="BB36" s="33"/>
+      <c r="BC36" s="33"/>
+      <c r="BD36" s="33"/>
+      <c r="BE36" s="33"/>
+      <c r="BF36" s="33"/>
+      <c r="BG36" s="33"/>
+      <c r="BH36" s="33"/>
+      <c r="BI36" s="33"/>
+      <c r="BJ36" s="33"/>
+      <c r="BK36" s="33"/>
+      <c r="BL36" s="33"/>
+      <c r="BM36" s="33"/>
+      <c r="BN36" s="33"/>
+      <c r="BO36" s="33"/>
+      <c r="BP36" s="33"/>
+      <c r="BQ36" s="33"/>
+      <c r="BR36" s="33"/>
+      <c r="BS36" s="33"/>
+      <c r="BT36" s="33"/>
+      <c r="BU36" s="34"/>
+    </row>
+    <row r="37" spans="1:73" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:73" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:73" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:73" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:73" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:73" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:73" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:73" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:73" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:73" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:73" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:73" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4476,85 +5179,85 @@
     <row r="62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="63" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="64" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="60:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="60:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="60:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="60:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="60:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="60:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="60:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="60:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="60:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="60:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="60:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="60:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="60:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="60:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="60:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BH79" s="11"/>
-      <c r="BI79" s="11"/>
-      <c r="BJ79" s="11"/>
+    <row r="65" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="59:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="59:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="59:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="59:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BH84" s="11"/>
+      <c r="BI84" s="11"/>
+      <c r="BJ84" s="11"/>
     </row>
-    <row r="80" spans="60:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BH80" s="11"/>
-      <c r="BI80" s="11"/>
-      <c r="BJ80" s="11"/>
-    </row>
-    <row r="81" spans="59:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BH81" s="11"/>
-      <c r="BI81" s="11"/>
-      <c r="BJ81" s="11"/>
-    </row>
-    <row r="82" spans="59:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BH82" s="11"/>
-      <c r="BI82" s="11"/>
-      <c r="BJ82" s="11"/>
-    </row>
-    <row r="83" spans="59:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BH83" s="11"/>
-      <c r="BI83" s="11"/>
-      <c r="BJ83" s="11"/>
-    </row>
-    <row r="84" spans="59:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="85" spans="59:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BG85" s="15"/>
-      <c r="BH85" s="15"/>
-      <c r="BI85" s="15"/>
-      <c r="BJ85" s="15"/>
+      <c r="BH85" s="11"/>
+      <c r="BI85" s="11"/>
+      <c r="BJ85" s="11"/>
     </row>
     <row r="86" spans="59:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BG86" s="15"/>
-      <c r="BH86" s="15"/>
-      <c r="BI86" s="15"/>
-      <c r="BJ86" s="15"/>
+      <c r="BH86" s="11"/>
+      <c r="BI86" s="11"/>
+      <c r="BJ86" s="11"/>
     </row>
     <row r="87" spans="59:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BG87" s="15"/>
-      <c r="BH87" s="15"/>
-      <c r="BI87" s="15"/>
-      <c r="BJ87" s="15"/>
+      <c r="BH87" s="11"/>
+      <c r="BI87" s="11"/>
+      <c r="BJ87" s="11"/>
     </row>
     <row r="88" spans="59:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BG88" s="15"/>
-      <c r="BH88" s="15"/>
-      <c r="BI88" s="15"/>
-      <c r="BJ88" s="15"/>
+      <c r="BH88" s="11"/>
+      <c r="BI88" s="11"/>
+      <c r="BJ88" s="11"/>
     </row>
-    <row r="89" spans="59:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BG89" s="15"/>
-      <c r="BH89" s="15"/>
-      <c r="BI89" s="15"/>
-      <c r="BJ89" s="15"/>
+    <row r="89" spans="59:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="59:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BG90" s="14"/>
+      <c r="BH90" s="14"/>
+      <c r="BI90" s="14"/>
+      <c r="BJ90" s="14"/>
     </row>
-    <row r="90" spans="59:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="59:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="59:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="59:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="59:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="59:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="59:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="59:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BG91" s="14"/>
+      <c r="BH91" s="14"/>
+      <c r="BI91" s="14"/>
+      <c r="BJ91" s="14"/>
+    </row>
+    <row r="92" spans="59:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BG92" s="14"/>
+      <c r="BH92" s="14"/>
+      <c r="BI92" s="14"/>
+      <c r="BJ92" s="14"/>
+    </row>
+    <row r="93" spans="59:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BG93" s="14"/>
+      <c r="BH93" s="14"/>
+      <c r="BI93" s="14"/>
+      <c r="BJ93" s="14"/>
+    </row>
+    <row r="94" spans="59:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BG94" s="14"/>
+      <c r="BH94" s="14"/>
+      <c r="BI94" s="14"/>
+      <c r="BJ94" s="14"/>
+    </row>
+    <row r="95" spans="59:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="59:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="60:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="60:62" ht="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="99" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="100" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="101" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4562,41 +5265,41 @@
     <row r="103" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="104" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="105" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="BH106" s="16"/>
-      <c r="BI106" s="16"/>
-      <c r="BJ106" s="16"/>
+    <row r="106" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="BH111" s="15"/>
+      <c r="BI111" s="15"/>
+      <c r="BJ111" s="15"/>
     </row>
-    <row r="107" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BH108" s="15"/>
-      <c r="BI108" s="15"/>
-      <c r="BJ108" s="15"/>
+    <row r="112" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BH113" s="14"/>
+      <c r="BI113" s="14"/>
+      <c r="BJ113" s="14"/>
     </row>
-    <row r="109" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BH109" s="15"/>
-      <c r="BI109" s="15"/>
-      <c r="BJ109" s="15"/>
+    <row r="114" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BH114" s="14"/>
+      <c r="BI114" s="14"/>
+      <c r="BJ114" s="14"/>
     </row>
-    <row r="110" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="60:62" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="60:62" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="60:62" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" spans="60:62" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" spans="60:62" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" spans="60:62" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" spans="60:62" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" spans="60:62" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" spans="60:62" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" spans="60:62" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="60:62" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="129" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="130" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="131" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7035,119 +7738,85 @@
     <row r="2564" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2565" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2566" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2567" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2568" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2569" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2570" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2571" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="207">
-    <mergeCell ref="BG13:BG16"/>
-    <mergeCell ref="BI13:BI16"/>
-    <mergeCell ref="BJ13:BJ16"/>
-    <mergeCell ref="J29:V30"/>
-    <mergeCell ref="H29:I30"/>
-    <mergeCell ref="BH27:BH30"/>
-    <mergeCell ref="BD18:BD22"/>
-    <mergeCell ref="BC18:BC22"/>
-    <mergeCell ref="AZ24:BS24"/>
-    <mergeCell ref="BS13:BS16"/>
-    <mergeCell ref="BE13:BE16"/>
-    <mergeCell ref="BS18:BS22"/>
-    <mergeCell ref="BR18:BR22"/>
-    <mergeCell ref="BQ18:BQ22"/>
-    <mergeCell ref="BP18:BP22"/>
-    <mergeCell ref="BO18:BO22"/>
-    <mergeCell ref="BN18:BN22"/>
-    <mergeCell ref="BM18:BM22"/>
-    <mergeCell ref="BL18:BL22"/>
-    <mergeCell ref="BK18:BK22"/>
-    <mergeCell ref="AI12:AI16"/>
-    <mergeCell ref="BL27:BL30"/>
-    <mergeCell ref="BN27:BN30"/>
-    <mergeCell ref="BS27:BS30"/>
-    <mergeCell ref="H7:I8"/>
-    <mergeCell ref="H9:I28"/>
-    <mergeCell ref="J9:V10"/>
-    <mergeCell ref="AZ27:AZ30"/>
-    <mergeCell ref="BB27:BB30"/>
-    <mergeCell ref="BF27:BF30"/>
-    <mergeCell ref="AQ13:AQ16"/>
-    <mergeCell ref="AB18:AB25"/>
-    <mergeCell ref="AA13:AA16"/>
-    <mergeCell ref="Z13:Z16"/>
-    <mergeCell ref="AL18:AL25"/>
-    <mergeCell ref="AM18:AM25"/>
-    <mergeCell ref="AC18:AC25"/>
-    <mergeCell ref="AD18:AD25"/>
-    <mergeCell ref="AG13:AG16"/>
-    <mergeCell ref="AC29:AL30"/>
-    <mergeCell ref="BF13:BF16"/>
-    <mergeCell ref="BC13:BC16"/>
-    <mergeCell ref="AK13:AK16"/>
-    <mergeCell ref="AF13:AF16"/>
-    <mergeCell ref="Y13:Y16"/>
-    <mergeCell ref="AP13:AP16"/>
-    <mergeCell ref="BQ27:BQ30"/>
-    <mergeCell ref="BI29:BK29"/>
-    <mergeCell ref="BI30:BK30"/>
-    <mergeCell ref="N18:N25"/>
-    <mergeCell ref="M18:M25"/>
-    <mergeCell ref="AF18:AF25"/>
-    <mergeCell ref="AG18:AG25"/>
-    <mergeCell ref="AH18:AH25"/>
-    <mergeCell ref="AU18:AU22"/>
-    <mergeCell ref="AO18:AO22"/>
-    <mergeCell ref="AI18:AI25"/>
-    <mergeCell ref="AJ18:AJ25"/>
-    <mergeCell ref="AK18:AK25"/>
-    <mergeCell ref="AP18:AP22"/>
-    <mergeCell ref="AQ18:AQ22"/>
-    <mergeCell ref="AR18:AR22"/>
-    <mergeCell ref="AS18:AS22"/>
-    <mergeCell ref="Y18:Y25"/>
-    <mergeCell ref="Z18:Z25"/>
-    <mergeCell ref="AA18:AA25"/>
-    <mergeCell ref="BE18:BE22"/>
-    <mergeCell ref="Y27:AU27"/>
-    <mergeCell ref="BB18:BB22"/>
-    <mergeCell ref="BA18:BA22"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="X18:X25"/>
-    <mergeCell ref="W18:W25"/>
-    <mergeCell ref="V18:V25"/>
-    <mergeCell ref="U18:U25"/>
-    <mergeCell ref="T18:T25"/>
-    <mergeCell ref="S18:S25"/>
-    <mergeCell ref="R18:R25"/>
-    <mergeCell ref="Q18:Q25"/>
-    <mergeCell ref="P18:P25"/>
-    <mergeCell ref="O18:O25"/>
-    <mergeCell ref="X13:X16"/>
-    <mergeCell ref="L18:L25"/>
-    <mergeCell ref="K18:K25"/>
-    <mergeCell ref="Z2:Z5"/>
-    <mergeCell ref="AD13:AD16"/>
-    <mergeCell ref="AC13:AC16"/>
-    <mergeCell ref="AB13:AB16"/>
-    <mergeCell ref="Q2:Q5"/>
-    <mergeCell ref="R2:R5"/>
-    <mergeCell ref="S2:S5"/>
-    <mergeCell ref="T2:T5"/>
-    <mergeCell ref="U2:U5"/>
-    <mergeCell ref="V2:V5"/>
-    <mergeCell ref="W7:AB7"/>
-    <mergeCell ref="W2:W5"/>
-    <mergeCell ref="AB2:AB5"/>
-    <mergeCell ref="AA2:AA5"/>
-    <mergeCell ref="X2:X5"/>
+  <mergeCells count="246">
+    <mergeCell ref="AL1:AP1"/>
+    <mergeCell ref="AD1:AJ1"/>
+    <mergeCell ref="W9:AL10"/>
+    <mergeCell ref="AZ18:AZ22"/>
+    <mergeCell ref="AE18:AE25"/>
+    <mergeCell ref="AC2:AC6"/>
+    <mergeCell ref="BJ18:BJ22"/>
+    <mergeCell ref="BI18:BI22"/>
+    <mergeCell ref="Y11:AU11"/>
+    <mergeCell ref="AT18:AT22"/>
+    <mergeCell ref="AW14:AX23"/>
+    <mergeCell ref="AU12:AU16"/>
+    <mergeCell ref="AY13:AY16"/>
+    <mergeCell ref="BA13:BA16"/>
+    <mergeCell ref="BB13:BB16"/>
+    <mergeCell ref="AZ13:AZ16"/>
+    <mergeCell ref="BD13:BD16"/>
+    <mergeCell ref="AZ2:AZ5"/>
+    <mergeCell ref="AY2:AY5"/>
+    <mergeCell ref="AN18:AN25"/>
+    <mergeCell ref="BH18:BH22"/>
+    <mergeCell ref="BG18:BG22"/>
+    <mergeCell ref="BF18:BF22"/>
+    <mergeCell ref="BE2:BE5"/>
+    <mergeCell ref="BR2:BR5"/>
+    <mergeCell ref="BQ2:BQ5"/>
+    <mergeCell ref="BP2:BP5"/>
+    <mergeCell ref="BO2:BO5"/>
+    <mergeCell ref="BN2:BN5"/>
+    <mergeCell ref="BM2:BM5"/>
+    <mergeCell ref="BR13:BR16"/>
+    <mergeCell ref="BQ13:BQ16"/>
+    <mergeCell ref="BP13:BP16"/>
+    <mergeCell ref="BM13:BM16"/>
+    <mergeCell ref="BN13:BN16"/>
+    <mergeCell ref="BO13:BO16"/>
+    <mergeCell ref="BG9:BP10"/>
+    <mergeCell ref="BB7:BR7"/>
+    <mergeCell ref="BH12:BH16"/>
+    <mergeCell ref="BK13:BK16"/>
+    <mergeCell ref="BL13:BL16"/>
+    <mergeCell ref="BL2:BL5"/>
+    <mergeCell ref="BK2:BK5"/>
+    <mergeCell ref="BJ2:BJ5"/>
+    <mergeCell ref="BI2:BI5"/>
+    <mergeCell ref="BH2:BH5"/>
+    <mergeCell ref="BG2:BG5"/>
+    <mergeCell ref="BF2:BF5"/>
+    <mergeCell ref="BD2:BD5"/>
+    <mergeCell ref="BC2:BC5"/>
+    <mergeCell ref="BB2:BB5"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="L2:L5"/>
+    <mergeCell ref="M2:M5"/>
+    <mergeCell ref="N2:N5"/>
+    <mergeCell ref="O2:O5"/>
+    <mergeCell ref="Y2:Y5"/>
+    <mergeCell ref="P2:P5"/>
+    <mergeCell ref="K2:K5"/>
+    <mergeCell ref="BA2:BA6"/>
+    <mergeCell ref="AJ2:AJ5"/>
+    <mergeCell ref="AS2:AS5"/>
+    <mergeCell ref="AR2:AR5"/>
+    <mergeCell ref="AQ2:AQ5"/>
+    <mergeCell ref="AP2:AP5"/>
+    <mergeCell ref="AN2:AN5"/>
+    <mergeCell ref="AO2:AO5"/>
+    <mergeCell ref="AD2:AD5"/>
+    <mergeCell ref="AE2:AE5"/>
+    <mergeCell ref="AF2:AF5"/>
     <mergeCell ref="AM2:AM5"/>
     <mergeCell ref="AN13:AN16"/>
     <mergeCell ref="AM13:AM16"/>
@@ -7172,81 +7841,159 @@
     <mergeCell ref="AJ13:AJ16"/>
     <mergeCell ref="AS13:AS16"/>
     <mergeCell ref="AT13:AT16"/>
-    <mergeCell ref="BD2:BD5"/>
-    <mergeCell ref="BC2:BC5"/>
-    <mergeCell ref="BB2:BB5"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="M1:O1"/>
-    <mergeCell ref="L2:L5"/>
-    <mergeCell ref="M2:M5"/>
-    <mergeCell ref="N2:N5"/>
-    <mergeCell ref="O2:O5"/>
-    <mergeCell ref="Y2:Y5"/>
-    <mergeCell ref="P2:P5"/>
-    <mergeCell ref="K2:K5"/>
-    <mergeCell ref="BA2:BA6"/>
-    <mergeCell ref="AJ2:AJ5"/>
-    <mergeCell ref="AS2:AS5"/>
-    <mergeCell ref="AR2:AR5"/>
-    <mergeCell ref="AQ2:AQ5"/>
-    <mergeCell ref="AP2:AP5"/>
-    <mergeCell ref="AN2:AN5"/>
-    <mergeCell ref="AO2:AO5"/>
-    <mergeCell ref="AD2:AD5"/>
-    <mergeCell ref="AE2:AE5"/>
-    <mergeCell ref="AF2:AF5"/>
-    <mergeCell ref="BR2:BR5"/>
-    <mergeCell ref="BQ2:BQ5"/>
-    <mergeCell ref="BP2:BP5"/>
-    <mergeCell ref="BO2:BO5"/>
-    <mergeCell ref="BN2:BN5"/>
-    <mergeCell ref="BM2:BM5"/>
-    <mergeCell ref="BR13:BR16"/>
-    <mergeCell ref="BQ13:BQ16"/>
-    <mergeCell ref="BP13:BP16"/>
-    <mergeCell ref="BM13:BM16"/>
-    <mergeCell ref="BN13:BN16"/>
-    <mergeCell ref="BO13:BO16"/>
-    <mergeCell ref="BG9:BP10"/>
-    <mergeCell ref="BB7:BR7"/>
-    <mergeCell ref="BH12:BH16"/>
-    <mergeCell ref="BK13:BK16"/>
-    <mergeCell ref="BL13:BL16"/>
-    <mergeCell ref="BL2:BL5"/>
-    <mergeCell ref="BK2:BK5"/>
-    <mergeCell ref="BJ2:BJ5"/>
-    <mergeCell ref="BI2:BI5"/>
-    <mergeCell ref="BH2:BH5"/>
-    <mergeCell ref="BG2:BG5"/>
-    <mergeCell ref="BF2:BF5"/>
-    <mergeCell ref="AL1:AP1"/>
-    <mergeCell ref="AD1:AJ1"/>
-    <mergeCell ref="W9:AL10"/>
-    <mergeCell ref="AZ18:AZ22"/>
-    <mergeCell ref="AE18:AE25"/>
-    <mergeCell ref="AC2:AC6"/>
-    <mergeCell ref="BJ18:BJ22"/>
-    <mergeCell ref="BI18:BI22"/>
-    <mergeCell ref="Y11:AU11"/>
-    <mergeCell ref="AT18:AT22"/>
-    <mergeCell ref="AW14:AX23"/>
-    <mergeCell ref="AU12:AU16"/>
-    <mergeCell ref="AY13:AY16"/>
-    <mergeCell ref="BA13:BA16"/>
-    <mergeCell ref="BB13:BB16"/>
-    <mergeCell ref="AZ13:AZ16"/>
-    <mergeCell ref="BD13:BD16"/>
-    <mergeCell ref="AZ2:AZ5"/>
-    <mergeCell ref="AY2:AY5"/>
-    <mergeCell ref="AN18:AN25"/>
-    <mergeCell ref="BH18:BH22"/>
-    <mergeCell ref="BG18:BG22"/>
-    <mergeCell ref="BF18:BF22"/>
-    <mergeCell ref="BE2:BE5"/>
+    <mergeCell ref="Z2:Z5"/>
+    <mergeCell ref="AD13:AD16"/>
+    <mergeCell ref="AC13:AC16"/>
+    <mergeCell ref="AB13:AB16"/>
+    <mergeCell ref="Q2:Q5"/>
+    <mergeCell ref="R2:R5"/>
+    <mergeCell ref="S2:S5"/>
+    <mergeCell ref="T2:T5"/>
+    <mergeCell ref="U2:U5"/>
+    <mergeCell ref="V2:V5"/>
+    <mergeCell ref="W7:AB7"/>
+    <mergeCell ref="W2:W5"/>
+    <mergeCell ref="AB2:AB5"/>
+    <mergeCell ref="AA2:AA5"/>
+    <mergeCell ref="X2:X5"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="X18:X25"/>
+    <mergeCell ref="W18:W25"/>
+    <mergeCell ref="V18:V25"/>
+    <mergeCell ref="U18:U25"/>
+    <mergeCell ref="T18:T25"/>
+    <mergeCell ref="S18:S25"/>
+    <mergeCell ref="R18:R25"/>
+    <mergeCell ref="Q18:Q25"/>
+    <mergeCell ref="P18:P25"/>
+    <mergeCell ref="O18:O25"/>
+    <mergeCell ref="X13:X16"/>
+    <mergeCell ref="L18:L25"/>
+    <mergeCell ref="K18:K25"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="H7:I8"/>
+    <mergeCell ref="H9:I28"/>
+    <mergeCell ref="J9:V10"/>
+    <mergeCell ref="AQ13:AQ16"/>
+    <mergeCell ref="AB18:AB25"/>
+    <mergeCell ref="AA13:AA16"/>
+    <mergeCell ref="Z13:Z16"/>
+    <mergeCell ref="AL18:AL25"/>
+    <mergeCell ref="AM18:AM25"/>
+    <mergeCell ref="AC18:AC25"/>
+    <mergeCell ref="AD18:AD25"/>
+    <mergeCell ref="AG13:AG16"/>
+    <mergeCell ref="AK13:AK16"/>
+    <mergeCell ref="AF13:AF16"/>
+    <mergeCell ref="Y13:Y16"/>
+    <mergeCell ref="AP13:AP16"/>
+    <mergeCell ref="N18:N25"/>
+    <mergeCell ref="M18:M25"/>
+    <mergeCell ref="AF18:AF25"/>
+    <mergeCell ref="AG18:AG25"/>
+    <mergeCell ref="AH18:AH25"/>
+    <mergeCell ref="AO18:AO22"/>
+    <mergeCell ref="AI18:AI25"/>
+    <mergeCell ref="AJ18:AJ25"/>
+    <mergeCell ref="H29:I30"/>
+    <mergeCell ref="BD18:BD22"/>
+    <mergeCell ref="BC18:BC22"/>
+    <mergeCell ref="AZ24:BS24"/>
+    <mergeCell ref="BS13:BS16"/>
+    <mergeCell ref="BE13:BE16"/>
+    <mergeCell ref="BS18:BS22"/>
+    <mergeCell ref="BR18:BR22"/>
+    <mergeCell ref="BQ18:BQ22"/>
+    <mergeCell ref="BP18:BP22"/>
+    <mergeCell ref="BO18:BO22"/>
+    <mergeCell ref="BN18:BN22"/>
+    <mergeCell ref="BM18:BM22"/>
+    <mergeCell ref="BL18:BL22"/>
+    <mergeCell ref="BK18:BK22"/>
+    <mergeCell ref="AI12:AI16"/>
+    <mergeCell ref="AC29:AL30"/>
+    <mergeCell ref="BF13:BF16"/>
+    <mergeCell ref="BC13:BC16"/>
+    <mergeCell ref="BI29:BK29"/>
+    <mergeCell ref="BI30:BK30"/>
+    <mergeCell ref="AU18:AU22"/>
+    <mergeCell ref="AK18:AK25"/>
+    <mergeCell ref="AP18:AP22"/>
+    <mergeCell ref="M32:M35"/>
+    <mergeCell ref="K32:K35"/>
+    <mergeCell ref="L32:L35"/>
+    <mergeCell ref="N32:N35"/>
+    <mergeCell ref="O32:O35"/>
+    <mergeCell ref="P32:P35"/>
+    <mergeCell ref="BG13:BG16"/>
+    <mergeCell ref="BI13:BI16"/>
+    <mergeCell ref="BJ13:BJ16"/>
+    <mergeCell ref="J29:V30"/>
+    <mergeCell ref="AQ18:AQ22"/>
+    <mergeCell ref="AR18:AR22"/>
+    <mergeCell ref="AS18:AS22"/>
+    <mergeCell ref="Y18:Y25"/>
+    <mergeCell ref="Z18:Z25"/>
+    <mergeCell ref="AA18:AA25"/>
+    <mergeCell ref="BE18:BE22"/>
+    <mergeCell ref="Y27:AU27"/>
+    <mergeCell ref="BB18:BB22"/>
+    <mergeCell ref="BA18:BA22"/>
+    <mergeCell ref="Q32:Q35"/>
+    <mergeCell ref="R32:R35"/>
+    <mergeCell ref="S32:S35"/>
+    <mergeCell ref="T32:T35"/>
+    <mergeCell ref="U32:U35"/>
+    <mergeCell ref="V32:V35"/>
+    <mergeCell ref="W32:W35"/>
+    <mergeCell ref="X32:X35"/>
+    <mergeCell ref="Y32:Y35"/>
+    <mergeCell ref="AI32:AI35"/>
+    <mergeCell ref="AJ32:AJ35"/>
+    <mergeCell ref="AK32:AK35"/>
+    <mergeCell ref="AL32:AL35"/>
+    <mergeCell ref="AM32:AM35"/>
+    <mergeCell ref="AN32:AN35"/>
+    <mergeCell ref="Z32:Z35"/>
+    <mergeCell ref="AA32:AA35"/>
+    <mergeCell ref="AB32:AB35"/>
+    <mergeCell ref="AC32:AC35"/>
+    <mergeCell ref="AD32:AD35"/>
+    <mergeCell ref="AE32:AE35"/>
+    <mergeCell ref="AF32:AF35"/>
+    <mergeCell ref="AG32:AG35"/>
+    <mergeCell ref="AH32:AH35"/>
+    <mergeCell ref="BT31:BT35"/>
+    <mergeCell ref="BR31:BR35"/>
+    <mergeCell ref="BO31:BP35"/>
+    <mergeCell ref="BM31:BM35"/>
+    <mergeCell ref="BI31:BK35"/>
+    <mergeCell ref="BG31:BG35"/>
+    <mergeCell ref="BC31:BE35"/>
+    <mergeCell ref="BA31:BA35"/>
+    <mergeCell ref="AO31:AV35"/>
+    <mergeCell ref="BF27:BF35"/>
+    <mergeCell ref="BS27:BS35"/>
+    <mergeCell ref="BQ27:BQ35"/>
+    <mergeCell ref="BN27:BN35"/>
+    <mergeCell ref="BL27:BL35"/>
+    <mergeCell ref="AZ27:AZ35"/>
+    <mergeCell ref="BB27:BB35"/>
+    <mergeCell ref="BH27:BH35"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="8" scale="33" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="8" scale="29" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>